--- a/GATEWAY/A1#111#WEBINARSRLXX/We_BiNar_S.r.l/wepacs/2.0/report-checklist.xlsx
+++ b/GATEWAY/A1#111#WEBINARSRLXX/We_BiNar_S.r.l/wepacs/2.0/report-checklist.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\projects\WeBinar\wepacs\misc\FSE\GATEWAY\A1#111#WEBINARSRLXX\We_BiNar_S.r.l\wepacs\2.0\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\projects\WeBinar\wepacs\misc\FSE\Sogei\RAD-RSA\GATEWAY\A1#111#WEBINARSRLXX\We_BiNar_S.r.l\wepacs\2.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{863DD754-27F3-4E50-9E8D-DBA34FA9B14A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1C270E0-E782-4C04-ABD4-55D07581079C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Summary!$A$1:$G$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">TestCases!$A$9:$W$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">TestCases!$A$9:$W$55</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="725" uniqueCount="311">
   <si>
     <t>COME VALORIZZARE LA CHECKLIST (tab TestCases)</t>
   </si>
@@ -690,184 +690,513 @@
     <t>Dati non validi o mancanti</t>
   </si>
   <si>
-    <t>2025-10-11T15:08:24Z</t>
-  </si>
-  <si>
-    <t>2025-10-11T15:08:25Z</t>
-  </si>
-  <si>
-    <t>2025-10-11T15:08:27Z</t>
-  </si>
-  <si>
-    <t>2025-10-11T15:08:28Z</t>
-  </si>
-  <si>
-    <t>2025-10-11T15:08:29Z</t>
-  </si>
-  <si>
-    <t>2025-10-11T15:08:31Z</t>
-  </si>
-  <si>
-    <t>2025-10-11T15:08:50Z</t>
-  </si>
-  <si>
-    <t>2025-10-11T15:09:02Z</t>
-  </si>
-  <si>
-    <t>2025-10-11T15:09:12Z</t>
-  </si>
-  <si>
-    <t>2025-10-11T15:09:16Z</t>
-  </si>
-  <si>
-    <t>2025-10-11T15:09:18Z</t>
-  </si>
-  <si>
-    <t>2025-10-11T15:09:25Z</t>
-  </si>
-  <si>
-    <t>2025-10-11T15:09:31Z</t>
-  </si>
-  <si>
-    <t>2025-10-11T15:09:42Z</t>
-  </si>
-  <si>
-    <t>2025-10-11T15:09:53Z</t>
-  </si>
-  <si>
-    <t>2025-10-11T15:10:00Z</t>
-  </si>
-  <si>
-    <t>2025-10-11T15:10:14Z</t>
-  </si>
-  <si>
-    <t>2025-10-11T15:10:38Z</t>
-  </si>
-  <si>
-    <t>cff61c1da6501378def6241926612109</t>
-  </si>
-  <si>
-    <t>ad4465d35e2e352638804072d5cfcba9</t>
-  </si>
-  <si>
-    <t>102e9f8e3f4978ca374a0c701424371a</t>
-  </si>
-  <si>
-    <t>0359f0d506c5a039f48b8ed7af621c3d</t>
-  </si>
-  <si>
-    <t>89258a7e35b16f44a89a1af6d047851e</t>
-  </si>
-  <si>
-    <t>dd19b18c83dad485e2815df90de34892</t>
-  </si>
-  <si>
-    <t>ac0ccfba8129ab58b276b5589384727c</t>
-  </si>
-  <si>
-    <t>c75238ed7e65db70d51f2d1e2d54ad49</t>
-  </si>
-  <si>
-    <t>4de9f0b02bc0aca25456643057861211</t>
-  </si>
-  <si>
-    <t>dbc9db8708905fb75ee08e5c94bec284</t>
-  </si>
-  <si>
-    <t>c42bbf3cd0b14e0316b61eacb1c3d68c</t>
-  </si>
-  <si>
-    <t>1496a8c692d440b1a58f5da1e997c3c6</t>
-  </si>
-  <si>
-    <t>3eb067284c13ccb54055ea3b77913d11</t>
-  </si>
-  <si>
-    <t>d9603f52c30c10ef347791566c85e270</t>
-  </si>
-  <si>
-    <t>b093b93451c7c4a414439cabb915badc</t>
-  </si>
-  <si>
-    <t>47fd7ac18bcbc61c682c77ccea480fa1</t>
-  </si>
-  <si>
-    <t>2a4871818dfc4ce3ff9c231f544d277e</t>
-  </si>
-  <si>
-    <t>0cb48b6d73babfac7f4afcce46425efb</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.150909.4.4.184b3a18a59460676130c9260beb03716dc2698d6c3a01481a7015704b19119d.111fc8b676^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.150909.4.4.cf854f200bb65a6083cfa839f9464e75582e8fe09d29db08d598e2bf5b08838e.206e0179ab^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.150909.4.4.7633ebfe119ee50d8b33d713dfad8f4fa23bf66408dacc69065a66297f702ce8.71d60ef64f^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.150909.4.4.14076e9b5a1565fc73506de948ac310ad19017609248f2f2ae270c3b446a49db.4dcde2be1c^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.150909.4.4.7e4c5cd37945b586d68e0309e0edb5cd32d6b68174110d68b8e2aff3f79b5c69.e03c230dc4^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.150909.4.4.7c0268b5fa7b8d3f5e40412c3c63555075cb7a62045ee4c6254cd3759a2286e1.db9bfd57a6^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.150909.4.4.95862c83d4c460fddce30172d86bb689668aa83a4848e09f94c3d5e78503d9a4.773d6fa2e3^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.150909.4.4.f7730a00c847a7bf80af4f12bca9f16a378e4a7a686e28cacd9aefb281dcd3f2.10a0d2fa79^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.150909.4.4.9a6d5ae243e44e9e949837dc634b9a73fae9985ed83a86801550ec77837091e6.73eb31320f^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.150909.4.4.f8e3f5065a2cce691db170231bd8b5ebb7b421925eef3e6a467370c6b5d0a322.fd500231b0^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.150909.4.4.ee2d920e008cdce9224a4a76f40a7562018f85d37d02349c89a1541ada18a2ef.78ae6eafc5^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.150909.4.4.d1e860d76d886637807e444f36e04c4771c4aa48c11a678006b8863863b5b82b.59d7f342e6^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.150909.4.4.ac9000e960fca89660e55d7c9429b2b45609042fb32dbf6ed67b8d9f6a6c1f5d.ba6b35c8bb^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.150909.4.4.91adf84d0a67385aa118e8de800a28a10c8d88d323608f3958da3ed99e0f3aae.38a12e2eb3^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.150909.4.4.ea4893b139a1dbdaba8659c2f080b76614b734cba6275c3900816458b6e813de.dbf100fdd7^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.150909.4.4.720d363c9b2df8f4b0cf2e0804d570a8cb5360c73f7a6e6af08ec5595f302d1b.bc97d6965f^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.150909.4.4.9df84cc65eaab96baebfa476fbb83534c42f2618775fe1896652fa960a2d2200.9d26a3435f^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.150909.4.4.25d5aa67979e69c78c46f05ceb80997f060ed271ed1171cc67d8589549fa4c26.129fe156ed^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2025-10-18T21:47:41Z</t>
-  </si>
-  <si>
-    <t>aa9671c090138b6faa11e3620b2cb866</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.150909.4.4.41a6f17bcd9c0a141a0d3e8589c695d1dbfa1e104d7bad5b149cd875fb5c35ad.37972fe81a^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2025-11-13T19:08:25Z</t>
-  </si>
-  <si>
-    <t>eb6cadfc90095804f4e29078b7ab80e5</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.150909.4.4.a6d85f5e79ae7f05470c88415b651b8d470f16047aba7a7d49e2dd17b20f6402.ed21d162a5^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>VALIDAZIONE_TOKEN_JWT_RSA_KO</t>
+  </si>
+  <si>
+    <t>VALIDAZIONE_TOKEN_JWT_CAMPO_RSA_KO</t>
+  </si>
+  <si>
+    <t>VALIDAZIONE_CDA2_RSA_CT28_KO</t>
+  </si>
+  <si>
+    <t>VALIDAZIONE_CDA2_RSA_CT6_KO</t>
+  </si>
+  <si>
+    <t>VALIDAZIONE_CDA2_RSA_CT8_KO</t>
+  </si>
+  <si>
+    <t>VALIDAZIONE_CDA2_RSA_CT9_KO</t>
+  </si>
+  <si>
+    <t>VALIDAZIONE_CDA2_RSA_CT10_KO</t>
+  </si>
+  <si>
+    <t>VALIDAZIONE_CDA2_RSA_CT13_KO</t>
+  </si>
+  <si>
+    <t>VALIDAZIONE_CDA2_RSA_CT14_KO</t>
+  </si>
+  <si>
+    <t>VALIDAZIONE_CDA2_RSA_CT15_KO</t>
+  </si>
+  <si>
+    <t>VALIDAZIONE_CDA2_RSA_CT16_KO</t>
+  </si>
+  <si>
+    <t>VALIDAZIONE_CDA2_RSA_CT17_KO</t>
+  </si>
+  <si>
+    <t>VALIDAZIONE_CDA2_RSA_CT18_KO</t>
+  </si>
+  <si>
+    <t>VALIDAZIONE_CDA2_RSA_CT19_KO</t>
+  </si>
+  <si>
+    <t>VALIDAZIONE_CDA2_RSA_CT20_KO</t>
+  </si>
+  <si>
+    <t>VALIDAZIONE_CDA2_RSA_CT21_KO</t>
+  </si>
+  <si>
+    <t>VALIDAZIONE_CDA2_RSA_CT22_KO</t>
+  </si>
+  <si>
+    <t>VALIDAZIONE_CDA2_RSA_CT23_KO</t>
+  </si>
+  <si>
+    <t>VALIDAZIONE_CDA2_RSA_CT24</t>
+  </si>
+  <si>
+    <t>VALIDAZIONE_CDA2_RSA_CT25</t>
+  </si>
+  <si>
+    <t>VALIDAZIONE_CDA2_RSA_CT26_KO</t>
+  </si>
+  <si>
+    <t>VALIDAZIONE_CDA2_RSA_CT27_KO</t>
+  </si>
+  <si>
+    <t>Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori semantici sui Dati (status code 422), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway. 
+I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 6" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
+  </si>
+  <si>
+    <t>Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori semantici sui Dati (status code 422), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway. 
+I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 8" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
+  </si>
+  <si>
+    <t>Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori semantici sui Dati (status code 422), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway. 
+I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 9" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
+  </si>
+  <si>
+    <t>Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori terminologici sui Dati (status code 400), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway.
+I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 10" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
+  </si>
+  <si>
+    <t>Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori sintattici sui Dati (status code 400), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway.
+I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 13" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
+  </si>
+  <si>
+    <t>Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori sintattici sui Dati (status code 400), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway.
+I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 14" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
+  </si>
+  <si>
+    <t>Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori semantici sui Dati (status code 422), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway. 
+I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 15" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
+  </si>
+  <si>
+    <t>Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori semantici sui Dati (status code 422), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway. 
+I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 16" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
+  </si>
+  <si>
+    <t>Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori semantici sui Dati (status code 422), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway. 
+I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 17" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
+  </si>
+  <si>
+    <t>Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori semantici sui Dati (status code 422), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway. 
+I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 18" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
+  </si>
+  <si>
+    <t>Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori semantici sui Dati (status code 422), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway. 
+I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 19" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
+  </si>
+  <si>
+    <t>Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori semantici sui Dati (status code 422), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway. 
+I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 20" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
+  </si>
+  <si>
+    <t>Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori semantici sui Dati (status code 422), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway. 
+I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 21" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
+  </si>
+  <si>
+    <t>Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori terminologici sui Dati (status code 400), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway.
+I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 22" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
+  </si>
+  <si>
+    <t>Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori semantici sui Dati (status code 422), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway. 
+I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 23" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
+  </si>
+  <si>
+    <t>Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation", al fine di una futura pubblicazione, con esito positivo (status code 201), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway.
+Il Documento CDA2 Referto Specialistica Ambulatoriale dovrà essere composto in modo da risultare valido dal punto di vista sintattico, semantico, terminologico. I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso dalla sezione "CASO DI TEST 24" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_OK" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
+  </si>
+  <si>
+    <t>Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation", al fine di una futura pubblicazione, con esito positivo (status code 201), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway.
+Il Documento CDA2 Referto Specialistica Ambulatoriale dovrà essere composto in modo da risultare valido dal punto di vista sintattico, semantico, terminologico. I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso dalla sezione "CASO DI TEST 25" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_OK" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
+  </si>
+  <si>
+    <t>Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori terminologici sui Dati (status code 400), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway. 
+I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 26" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
+  </si>
+  <si>
+    <t>Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori sintattici sui Dati (status code 400), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway.
+I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 27" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
+  </si>
+  <si>
+    <t>Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori terminologici sui Dati (status code 400), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway. 
+I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 28" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
+  </si>
+  <si>
+    <t>VALIDAZIONE_RSA_TIMEOUT</t>
+  </si>
+  <si>
+    <t>2026-04-28T15:56:18Z</t>
+  </si>
+  <si>
+    <t>2026-04-28T15:56:21Z</t>
+  </si>
+  <si>
+    <t>2026-04-28T15:56:24Z</t>
+  </si>
+  <si>
+    <t>2026-04-28T15:56:26Z</t>
+  </si>
+  <si>
+    <t>2026-04-28T15:56:40Z</t>
+  </si>
+  <si>
+    <t>2026-04-28T15:56:48Z</t>
+  </si>
+  <si>
+    <t>2026-04-28T15:56:56Z</t>
+  </si>
+  <si>
+    <t>2026-04-28T15:57:11Z</t>
+  </si>
+  <si>
+    <t>2026-04-28T15:57:18Z</t>
+  </si>
+  <si>
+    <t>2026-04-28T15:57:24Z</t>
+  </si>
+  <si>
+    <t>2026-04-28T15:57:41Z</t>
+  </si>
+  <si>
+    <t>2026-04-28T15:57:49Z</t>
+  </si>
+  <si>
+    <t>2026-04-28T15:58:00Z</t>
+  </si>
+  <si>
+    <t>2026-04-28T15:58:05Z</t>
+  </si>
+  <si>
+    <t>2026-04-28T15:58:13Z</t>
+  </si>
+  <si>
+    <t>2026-04-28T15:58:21Z</t>
+  </si>
+  <si>
+    <t>2026-04-28T15:58:29Z</t>
+  </si>
+  <si>
+    <t>2026-04-28T15:58:42Z</t>
+  </si>
+  <si>
+    <t>2026-04-28T15:58:46Z</t>
+  </si>
+  <si>
+    <t>2026-04-28T15:58:53Z</t>
+  </si>
+  <si>
+    <t>acb8951e136580d5cb74d8922dfe06ce</t>
+  </si>
+  <si>
+    <t>a2cea835202a147aac326a7a2d55f896</t>
+  </si>
+  <si>
+    <t>3e97186150a50b8c848eb417ee160330</t>
+  </si>
+  <si>
+    <t>0aea24e372f4f0083a51fbda8a6a5c5d</t>
+  </si>
+  <si>
+    <t>d5051326a63f9e60bc7a654c7bc69a51</t>
+  </si>
+  <si>
+    <t>6421dd634867c751823498508de31f21</t>
+  </si>
+  <si>
+    <t>3a6c34c6ca89b71f778f6e407f23c56c</t>
+  </si>
+  <si>
+    <t>cead87c2c28fc8174959a8e609153f19</t>
+  </si>
+  <si>
+    <t>fed57bc91220af56c0d7541784436896</t>
+  </si>
+  <si>
+    <t>ed747d32ff50b3630b14d8d1d8663f59</t>
+  </si>
+  <si>
+    <t>2f515008f56d2e7bdd86282991eec624</t>
+  </si>
+  <si>
+    <t>a41b700a0fb006f346ce62bfc9611328</t>
+  </si>
+  <si>
+    <t>d4972bbfafd41d02fc792d4e3f91b6bf</t>
+  </si>
+  <si>
+    <t>e27500adf2b823328d5fdeeca432a269</t>
+  </si>
+  <si>
+    <t>affc42c45fb2d1a9a41ffc0cdaf711df</t>
+  </si>
+  <si>
+    <t>2a01db8580e6100dd94b4c6b46228ea0</t>
+  </si>
+  <si>
+    <t>7080f98e966b82fade1739c57b088bf6</t>
+  </si>
+  <si>
+    <t>8dc2ab5a9bc78e5f3fafad46ce7db2f0</t>
+  </si>
+  <si>
+    <t>97eec55039ae84f3270a012bd6147650</t>
+  </si>
+  <si>
+    <t>0d5475b430abebf683eedcb0e79328e4</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.150909.4.4.c1c46882c39ab7f1f0c14ebe267b6893d906f02fb61729139f9bf8b80dc84dc5.d28464c515^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.150909.4.4.651c6b3881bba413e0e430a96c7b1206c39776f2a37eb29fe133cb1e34dcfbd3.2c5cc85fcf^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.150909.4.4.61ea86d83a86b4f397e444e467d682be990d20768008a852b830f67375fa6c6a.b1b81f6627^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.150909.4.4.c34ef629f57f6066e913d97c324344ba7280fb84dbb133bbd08df55843556510.f92078ace1^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.150909.4.4.1e1ac2e0d6fcc956321cf0f5a139755ced275dd232879c4f9e295e7a1c81f7a9.cdebcc3b72^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.150909.4.4.22f318d3356d7006d03fa96c675259e73597bcf840b595be3d5c0639ec1fe823.8bfe5edfaf^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.150909.4.4.edb15d7b9fbc05a9905ce6b8495e0c65a1fec403293f1ead5abcba52beb2875b.f0a14f57ea^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.150909.4.4.07e024565fdfdcac1594995b92770c8ac277fb27caad38d11c7819483b871679.3f8590b3e9^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.150909.4.4.8ef27e04779288c04d52c1b18895aee5355128425d8c8708b1687e9fbe44273f.ed01e84b5e^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.150909.4.4.c74dc46be13ea67f164ec2d163929ba31e1864b4c9ee082dd1a9aa836583817a.6eb4054ff2^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.150909.4.4.ead41fe5538c47bee4fa8d82b713d1f553b2b9d60732807e4a2f401e104745b9.925f6ca512^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.150909.4.4.2158783158e12fef212c5db229ccb26250b1b0c33f1046d50f882b2a449d91a5.302f76bd44^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.150909.4.4.526e2afa8c2709e4120c5ac3bbc1dc6ff935651306099da92a0cfd98ab39469d.3bd24cc73c^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.150909.4.4.3816f15cdfa75569d606fea3e6c2e6a8bd74520fc8a9db2eaca2b7403826e031.c27f4c5191^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.150909.4.4.74d487c4c06748a50c5dbc9efd0e1b40dbe5fca49c1eab8479b38e27683b63f1.dea0d328d5^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.150909.4.4.80a9381cb86b9433dafeff00a308c3f00d69f9361f1f8445ff4ebc5331aa876c.3a3f3bce3e^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.150909.4.4.6fb24cde69d026b38ca8ee4aa0a5314e9a794471bb8eef3ac6fd6e267045f0c8.fa4d7d7165^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.150909.4.4.6a476287610ea1e56168a9a0712acf27e50367993d0be47bb7413adcb8bea0a2.646b7d7295^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.150909.4.4.a1671eeb59bc2a40e484923ef701ee5599ed601120816a8269f80c4c05d93f25.57653774fc^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.150909.4.4.b79159e183f100a3be87acf5d57249bdc0b769f3ef0fb124aea7e8e68cee2e6e.4284dad025^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2026-04-28T14:43:53Z</t>
+  </si>
+  <si>
+    <t>2026-04-28T14:43:59Z</t>
+  </si>
+  <si>
+    <t>2026-04-28T14:44:05Z</t>
+  </si>
+  <si>
+    <t>2026-04-28T14:44:06Z</t>
+  </si>
+  <si>
+    <t>2026-04-28T14:44:10Z</t>
+  </si>
+  <si>
+    <t>2026-04-28T14:44:14Z</t>
+  </si>
+  <si>
+    <t>2026-04-28T14:44:16Z</t>
+  </si>
+  <si>
+    <t>2026-04-28T14:44:19Z</t>
+  </si>
+  <si>
+    <t>2026-04-28T14:44:22Z</t>
+  </si>
+  <si>
+    <t>2026-04-28T14:44:26Z</t>
+  </si>
+  <si>
+    <t>2026-04-28T14:44:31Z</t>
+  </si>
+  <si>
+    <t>2026-04-28T14:44:35Z</t>
+  </si>
+  <si>
+    <t>2026-04-28T14:44:39Z</t>
+  </si>
+  <si>
+    <t>2026-04-28T14:44:43Z</t>
+  </si>
+  <si>
+    <t>2026-04-28T14:44:46Z</t>
+  </si>
+  <si>
+    <t>2026-04-28T14:44:50Z</t>
+  </si>
+  <si>
+    <t>2026-04-28T14:44:55Z</t>
+  </si>
+  <si>
+    <t>2026-04-28T14:44:58Z</t>
+  </si>
+  <si>
+    <t>2026-04-28T14:45:02Z</t>
+  </si>
+  <si>
+    <t>2026-04-28T14:45:06Z</t>
+  </si>
+  <si>
+    <t>5d330f4416dbae5867cce25b73a9287d</t>
+  </si>
+  <si>
+    <t>9ff62860babd767a36b588b41db9a3ba</t>
+  </si>
+  <si>
+    <t>117b3094e87aa12ade14f2310fc8c0ad</t>
+  </si>
+  <si>
+    <t>31a93af112abd76941b50fac30b49031</t>
+  </si>
+  <si>
+    <t>89795683580e43ebfa419c052fca0895</t>
+  </si>
+  <si>
+    <t>9bd7b37569532eb46b50716b990dd35a</t>
+  </si>
+  <si>
+    <t>48854f7a28b56574e021e96531df15ef</t>
+  </si>
+  <si>
+    <t>f3e46366b71dca23ddefe0fd8ac6308a</t>
+  </si>
+  <si>
+    <t>1664501e12b9726398c2e5a6985dcf97</t>
+  </si>
+  <si>
+    <t>1f672ab611ba53ccd703557a0cf5bf04</t>
+  </si>
+  <si>
+    <t>82411b068c2f632a7e844a4a02bed5f2</t>
+  </si>
+  <si>
+    <t>71855a020836b93f3092d966cbb05239</t>
+  </si>
+  <si>
+    <t>95dc09d4fc92a0229e12a71f956015dd</t>
+  </si>
+  <si>
+    <t>5bfa72fb37fe7a34274f5210ea8afc00</t>
+  </si>
+  <si>
+    <t>6bd35c6a5fd9a8610d28b993a8811d1a</t>
+  </si>
+  <si>
+    <t>8c451d449262dd44f07209a92747aba3</t>
+  </si>
+  <si>
+    <t>ae4d2edb509610cacc8d2c24b56cacd0</t>
+  </si>
+  <si>
+    <t>80f73d85d3b9eaeeda9265492fe21523</t>
+  </si>
+  <si>
+    <t>f120da51f83e09dec07570f4fdad35f3</t>
+  </si>
+  <si>
+    <t>9ee2fee3d5472a97fa79b1e24cb415cf</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.150909.4.4.b02a24ff06da39338340edc1e22155567dfff8cc59e3a0eb210488604a6f3ff8.46d0c80864^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.150909.4.4.53df44443c03ddb4f8e053386799cdd490f7985d7a3933257f0d922f518292f1.fb7dddb52c^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.150909.4.4.b2169ddc0d6e2a5b55101d3e2eaf8ab1db0779b0faf977f3878e0f577161fc73.6aadc2d28c^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.150909.4.4.3daf0c7af83c37b706278ec6545dbe3636c2e67f7e8aa5a0623ec5687750c71b.72778f16f3^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.150909.4.4.f059af14b0d69336a1c7c98060b603a34841a9ebfa9d903204dbcfe44877da53.93b75ab05c^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.150909.4.4.5663724eb0b6e0f54b5845ed5b14cd3a3e80dc37bb34a1d3c7d9dd8c350a2cf3.4505ddd251^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.150909.4.4.c802d822f85cf2344da2b88a431553c29a6baa03f52df0517f9b62824e5ab001.da85c98b7d^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.150909.4.4.dd5061c4d003a96c394b7820203950d461acab868c52dcd352a19433cae2528b.6e5ac6effc^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.150909.4.4.ab2031f38bc2e1c831a1554de21a56db0e937b1c91e53f0622faf39297e5c3ff.241a5c2f01^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.150909.4.4.90df5350981a03e5267a5353654e9abb5bbadab23e252abf326772ee4de064b8.33c272b0c7^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.150909.4.4.367f27b3331e05d775e0c7898504d4580a3e5f4328b8458cdcd0f75c0dd2bd49.cf63d7a19a^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.150909.4.4.51d2eefb936f6ffc55a36b5985c01479a93f8a14d0d522f3144a40346e6f6af8.d2f49fd7bf^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.150909.4.4.eafa4e8a0d9ad81a69bddb21ef8005432fae1539a77fb9e65011d43413cd3b88.d8a206a7d0^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.150909.4.4.51dc8da407a32f85ca39cc21c5846ccf8a438000a1c535c5d066fd6a96c568a2.951f5b4045^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.150909.4.4.5d9c8376b3444265ce2257ace9839b7e307014e4ffd9d9d37343e63e50343da3.c6b88738ef^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.150909.4.4.943a2ca6f26f23120e8532bb3cabef41b0669a9492a1444a897d3eb980ffdf46.56e6a486ec^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.150909.4.4.64ccc59d81535038f66c6f9e185aa726b3821822f09293151572db8f42f6579d.fd10dfdbe5^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.150909.4.4.3373f02e0ede5f64e57805ff701c32ca4f69f2d19f3dda7c10632dd0616b0868.410ffd41ec^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.150909.4.4.451d05c5974d2c9172aa551ef080ec29315dd3db65f36fcc6fad9ec8f98edaf3.d6e9524275^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.150909.4.4.53bea399799ddf046e5321230e7dd6f17b2242357303eb04fcbae34a6f9236d8.ddab1cf490^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
 </sst>
 </file>
@@ -877,7 +1206,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="d/m/yyyy"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -994,8 +1323,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1012,6 +1346,12 @@
       <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1316,7 +1656,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1427,8 +1767,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1451,6 +1797,9 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2889,7 +3238,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:W566"/>
+  <dimension ref="A1:W588"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" customWidth="1"/>
@@ -2931,14 +3280,14 @@
       <c r="W1" s="9"/>
     </row>
     <row r="2" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="47" t="s">
+      <c r="B2" s="48"/>
+      <c r="C2" s="49" t="s">
         <v>144</v>
       </c>
-      <c r="D2" s="46"/>
+      <c r="D2" s="48"/>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
       <c r="H2" s="6"/>
@@ -2959,14 +3308,14 @@
       <c r="W2" s="9"/>
     </row>
     <row r="3" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="48" t="s">
+      <c r="A3" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="49"/>
-      <c r="C3" s="54" t="s">
+      <c r="B3" s="51"/>
+      <c r="C3" s="56" t="s">
         <v>141</v>
       </c>
-      <c r="D3" s="46"/>
+      <c r="D3" s="48"/>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
       <c r="H3" s="6"/>
@@ -2987,12 +3336,12 @@
       <c r="W3" s="9"/>
     </row>
     <row r="4" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="50"/>
-      <c r="B4" s="51"/>
-      <c r="C4" s="54" t="s">
+      <c r="A4" s="52"/>
+      <c r="B4" s="53"/>
+      <c r="C4" s="56" t="s">
         <v>142</v>
       </c>
-      <c r="D4" s="46"/>
+      <c r="D4" s="48"/>
       <c r="E4" s="4"/>
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
@@ -3014,12 +3363,12 @@
       <c r="W4" s="9"/>
     </row>
     <row r="5" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="52"/>
-      <c r="B5" s="53"/>
-      <c r="C5" s="54" t="s">
+      <c r="A5" s="54"/>
+      <c r="B5" s="55"/>
+      <c r="C5" s="56" t="s">
         <v>143</v>
       </c>
-      <c r="D5" s="46"/>
+      <c r="D5" s="48"/>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
@@ -3040,8 +3389,8 @@
       <c r="W5" s="9"/>
     </row>
     <row r="6" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="43"/>
-      <c r="B6" s="44"/>
+      <c r="A6" s="45"/>
+      <c r="B6" s="46"/>
       <c r="C6" s="10"/>
       <c r="F6" s="6"/>
       <c r="G6" s="6"/>
@@ -3177,7 +3526,7 @@
       </c>
     </row>
     <row r="10" spans="1:23" ht="150.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="33">
+      <c r="A10" s="57">
         <v>31</v>
       </c>
       <c r="B10" s="33" t="s">
@@ -3217,21 +3566,21 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:23" ht="170.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="33">
-        <v>39</v>
+    <row r="11" spans="1:23" ht="150.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="57">
+        <v>32</v>
       </c>
       <c r="B11" s="33" t="s">
         <v>34</v>
       </c>
       <c r="C11" s="38" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" s="33" t="s">
-        <v>137</v>
+        <v>45</v>
+      </c>
+      <c r="D11" s="42" t="s">
+        <v>148</v>
       </c>
       <c r="E11" s="40" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F11" s="34"/>
       <c r="G11" s="34"/>
@@ -3240,8 +3589,8 @@
       <c r="J11" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="K11" s="35" t="s">
-        <v>64</v>
+      <c r="K11" s="44" t="s">
+        <v>61</v>
       </c>
       <c r="L11" s="35"/>
       <c r="M11" s="35"/>
@@ -3258,9 +3607,9 @@
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="1:23" ht="170.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="33">
-        <v>47</v>
+    <row r="12" spans="1:23" ht="165.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="57">
+        <v>39</v>
       </c>
       <c r="B12" s="33" t="s">
         <v>34</v>
@@ -3269,104 +3618,70 @@
         <v>38</v>
       </c>
       <c r="D12" s="33" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E12" s="40" t="s">
-        <v>93</v>
+        <v>46</v>
       </c>
       <c r="F12" s="34"/>
-      <c r="G12" s="42"/>
+      <c r="G12" s="34"/>
       <c r="H12" s="34"/>
-      <c r="I12" s="34"/>
+      <c r="I12" s="39"/>
       <c r="J12" s="35" t="s">
-        <v>47</v>
-      </c>
-      <c r="K12" s="35"/>
+        <v>56</v>
+      </c>
+      <c r="K12" s="35" t="s">
+        <v>64</v>
+      </c>
       <c r="L12" s="35"/>
-      <c r="M12" s="35" t="s">
-        <v>56</v>
-      </c>
-      <c r="N12" s="35" t="s">
-        <v>47</v>
-      </c>
-      <c r="O12" s="35" t="s">
-        <v>146</v>
-      </c>
-      <c r="P12" s="35" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q12" s="35" t="s">
-        <v>47</v>
-      </c>
-      <c r="R12" s="35" t="s">
-        <v>47</v>
-      </c>
-      <c r="S12" s="35" t="s">
-        <v>145</v>
-      </c>
+      <c r="M12" s="35"/>
+      <c r="N12" s="35"/>
+      <c r="O12" s="35"/>
+      <c r="P12" s="35"/>
+      <c r="Q12" s="35"/>
+      <c r="R12" s="35"/>
+      <c r="S12" s="35"/>
       <c r="T12" s="35"/>
-      <c r="U12" s="36" t="s">
-        <v>47</v>
-      </c>
+      <c r="U12" s="36"/>
       <c r="V12" s="37"/>
       <c r="W12" s="35" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="1:23" ht="170.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="33">
-        <v>76</v>
+    <row r="13" spans="1:23" ht="165.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="57">
+        <v>40</v>
       </c>
       <c r="B13" s="33" t="s">
         <v>34</v>
       </c>
       <c r="C13" s="38" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="D13" s="33" t="s">
-        <v>98</v>
+        <v>149</v>
       </c>
       <c r="E13" s="40" t="s">
-        <v>99</v>
-      </c>
-      <c r="F13" s="34">
-        <v>45941</v>
-      </c>
-      <c r="G13" s="34" t="s">
-        <v>148</v>
-      </c>
-      <c r="H13" s="34" t="s">
-        <v>166</v>
-      </c>
-      <c r="I13" s="39" t="s">
-        <v>184</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="F13" s="34"/>
+      <c r="G13" s="34"/>
+      <c r="H13" s="34"/>
+      <c r="I13" s="39"/>
       <c r="J13" s="35" t="s">
-        <v>47</v>
-      </c>
-      <c r="K13" s="35"/>
+        <v>56</v>
+      </c>
+      <c r="K13" s="35" t="s">
+        <v>64</v>
+      </c>
       <c r="L13" s="35"/>
-      <c r="M13" s="35" t="s">
-        <v>56</v>
-      </c>
-      <c r="N13" s="35" t="s">
-        <v>47</v>
-      </c>
-      <c r="O13" s="35" t="s">
-        <v>147</v>
-      </c>
-      <c r="P13" s="35" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q13" s="35" t="s">
-        <v>56</v>
-      </c>
-      <c r="R13" s="35" t="s">
-        <v>47</v>
-      </c>
-      <c r="S13" s="35" t="s">
-        <v>97</v>
-      </c>
+      <c r="M13" s="35"/>
+      <c r="N13" s="35"/>
+      <c r="O13" s="35"/>
+      <c r="P13" s="35"/>
+      <c r="Q13" s="35"/>
+      <c r="R13" s="35"/>
+      <c r="S13" s="35"/>
       <c r="T13" s="35"/>
       <c r="U13" s="36"/>
       <c r="V13" s="37"/>
@@ -3374,9 +3689,9 @@
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:23" ht="170.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="33">
-        <v>78</v>
+    <row r="14" spans="1:23" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="57">
+        <v>47</v>
       </c>
       <c r="B14" s="33" t="s">
         <v>34</v>
@@ -3385,23 +3700,15 @@
         <v>38</v>
       </c>
       <c r="D14" s="33" t="s">
-        <v>100</v>
+        <v>138</v>
       </c>
       <c r="E14" s="40" t="s">
-        <v>101</v>
-      </c>
-      <c r="F14" s="34">
-        <v>45941</v>
-      </c>
-      <c r="G14" s="34" t="s">
-        <v>149</v>
-      </c>
-      <c r="H14" s="34" t="s">
-        <v>167</v>
-      </c>
-      <c r="I14" s="39" t="s">
-        <v>185</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="F14" s="34"/>
+      <c r="G14" s="34"/>
+      <c r="H14" s="34"/>
+      <c r="I14" s="34"/>
       <c r="J14" s="35" t="s">
         <v>47</v>
       </c>
@@ -3414,55 +3721,49 @@
         <v>47</v>
       </c>
       <c r="O14" s="35" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P14" s="35" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="Q14" s="35" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="R14" s="35" t="s">
         <v>47</v>
       </c>
       <c r="S14" s="35" t="s">
-        <v>97</v>
+        <v>145</v>
       </c>
       <c r="T14" s="35"/>
-      <c r="U14" s="36"/>
+      <c r="U14" s="36" t="s">
+        <v>47</v>
+      </c>
       <c r="V14" s="37"/>
       <c r="W14" s="35" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="15" spans="1:23" ht="170.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="33">
-        <v>79</v>
+    <row r="15" spans="1:23" ht="106.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="57">
+        <v>48</v>
       </c>
       <c r="B15" s="33" t="s">
         <v>34</v>
       </c>
       <c r="C15" s="38" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="D15" s="33" t="s">
-        <v>102</v>
+        <v>190</v>
       </c>
       <c r="E15" s="40" t="s">
-        <v>103</v>
-      </c>
-      <c r="F15" s="34">
-        <v>45941</v>
-      </c>
-      <c r="G15" s="34" t="s">
-        <v>150</v>
-      </c>
-      <c r="H15" s="34" t="s">
-        <v>168</v>
-      </c>
-      <c r="I15" s="39" t="s">
-        <v>186</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="F15" s="34"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="34"/>
+      <c r="I15" s="39"/>
       <c r="J15" s="35" t="s">
         <v>47</v>
       </c>
@@ -3475,30 +3776,32 @@
         <v>47</v>
       </c>
       <c r="O15" s="35" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P15" s="35" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="Q15" s="35" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="R15" s="35" t="s">
         <v>47</v>
       </c>
       <c r="S15" s="35" t="s">
-        <v>97</v>
+        <v>145</v>
       </c>
       <c r="T15" s="35"/>
-      <c r="U15" s="36"/>
+      <c r="U15" s="36" t="s">
+        <v>47</v>
+      </c>
       <c r="V15" s="37"/>
       <c r="W15" s="35" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="1:23" ht="170.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="33">
-        <v>80</v>
+    <row r="16" spans="1:23" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="57">
+        <v>76</v>
       </c>
       <c r="B16" s="33" t="s">
         <v>34</v>
@@ -3507,22 +3810,22 @@
         <v>38</v>
       </c>
       <c r="D16" s="33" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E16" s="40" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="F16" s="34">
-        <v>45941</v>
+        <v>46140</v>
       </c>
       <c r="G16" s="34" t="s">
-        <v>151</v>
+        <v>191</v>
       </c>
       <c r="H16" s="34" t="s">
-        <v>169</v>
+        <v>211</v>
       </c>
       <c r="I16" s="39" t="s">
-        <v>187</v>
+        <v>231</v>
       </c>
       <c r="J16" s="35" t="s">
         <v>47</v>
@@ -3557,9 +3860,9 @@
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="1:23" ht="170.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="33">
-        <v>81</v>
+    <row r="17" spans="1:23" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="57">
+        <v>78</v>
       </c>
       <c r="B17" s="33" t="s">
         <v>34</v>
@@ -3568,22 +3871,22 @@
         <v>38</v>
       </c>
       <c r="D17" s="33" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E17" s="40" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="F17" s="34">
-        <v>45941</v>
+        <v>46140</v>
       </c>
       <c r="G17" s="34" t="s">
-        <v>152</v>
+        <v>192</v>
       </c>
       <c r="H17" s="34" t="s">
-        <v>170</v>
+        <v>212</v>
       </c>
       <c r="I17" s="39" t="s">
-        <v>188</v>
+        <v>232</v>
       </c>
       <c r="J17" s="35" t="s">
         <v>47</v>
@@ -3618,9 +3921,9 @@
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:23" ht="170.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="33">
-        <v>83</v>
+    <row r="18" spans="1:23" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="57">
+        <v>79</v>
       </c>
       <c r="B18" s="33" t="s">
         <v>34</v>
@@ -3629,22 +3932,22 @@
         <v>38</v>
       </c>
       <c r="D18" s="33" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="E18" s="40" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="F18" s="34">
-        <v>45941</v>
+        <v>46140</v>
       </c>
       <c r="G18" s="34" t="s">
-        <v>153</v>
+        <v>193</v>
       </c>
       <c r="H18" s="34" t="s">
-        <v>171</v>
+        <v>213</v>
       </c>
       <c r="I18" s="39" t="s">
-        <v>189</v>
+        <v>233</v>
       </c>
       <c r="J18" s="35" t="s">
         <v>47</v>
@@ -3679,9 +3982,9 @@
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="1:23" ht="170.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="33">
-        <v>84</v>
+    <row r="19" spans="1:23" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="57">
+        <v>80</v>
       </c>
       <c r="B19" s="33" t="s">
         <v>34</v>
@@ -3690,22 +3993,22 @@
         <v>38</v>
       </c>
       <c r="D19" s="33" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="E19" s="40" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="F19" s="34">
-        <v>45941</v>
+        <v>46140</v>
       </c>
       <c r="G19" s="34" t="s">
-        <v>154</v>
+        <v>194</v>
       </c>
       <c r="H19" s="34" t="s">
-        <v>172</v>
+        <v>214</v>
       </c>
       <c r="I19" s="39" t="s">
-        <v>190</v>
+        <v>234</v>
       </c>
       <c r="J19" s="35" t="s">
         <v>47</v>
@@ -3740,9 +4043,9 @@
         <v>43</v>
       </c>
     </row>
-    <row r="20" spans="1:23" ht="170.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="33">
-        <v>85</v>
+    <row r="20" spans="1:23" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="57">
+        <v>81</v>
       </c>
       <c r="B20" s="33" t="s">
         <v>34</v>
@@ -3751,22 +4054,22 @@
         <v>38</v>
       </c>
       <c r="D20" s="33" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="E20" s="40" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="F20" s="34">
-        <v>45941</v>
+        <v>46140</v>
       </c>
       <c r="G20" s="34" t="s">
-        <v>155</v>
+        <v>195</v>
       </c>
       <c r="H20" s="34" t="s">
-        <v>173</v>
+        <v>215</v>
       </c>
       <c r="I20" s="39" t="s">
-        <v>191</v>
+        <v>235</v>
       </c>
       <c r="J20" s="35" t="s">
         <v>47</v>
@@ -3801,9 +4104,9 @@
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:23" ht="170.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="33">
-        <v>86</v>
+    <row r="21" spans="1:23" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="57">
+        <v>83</v>
       </c>
       <c r="B21" s="33" t="s">
         <v>34</v>
@@ -3812,22 +4115,22 @@
         <v>38</v>
       </c>
       <c r="D21" s="33" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="E21" s="40" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="F21" s="34">
-        <v>45941</v>
+        <v>46140</v>
       </c>
       <c r="G21" s="34" t="s">
-        <v>156</v>
+        <v>196</v>
       </c>
       <c r="H21" s="34" t="s">
-        <v>174</v>
+        <v>216</v>
       </c>
       <c r="I21" s="39" t="s">
-        <v>192</v>
+        <v>236</v>
       </c>
       <c r="J21" s="35" t="s">
         <v>47</v>
@@ -3862,9 +4165,9 @@
         <v>43</v>
       </c>
     </row>
-    <row r="22" spans="1:23" ht="170.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="33">
-        <v>87</v>
+    <row r="22" spans="1:23" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="57">
+        <v>84</v>
       </c>
       <c r="B22" s="33" t="s">
         <v>34</v>
@@ -3873,22 +4176,22 @@
         <v>38</v>
       </c>
       <c r="D22" s="33" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="E22" s="40" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="F22" s="34">
-        <v>45941</v>
+        <v>46140</v>
       </c>
       <c r="G22" s="34" t="s">
-        <v>157</v>
+        <v>197</v>
       </c>
       <c r="H22" s="34" t="s">
-        <v>175</v>
+        <v>217</v>
       </c>
       <c r="I22" s="39" t="s">
-        <v>193</v>
+        <v>237</v>
       </c>
       <c r="J22" s="35" t="s">
         <v>47</v>
@@ -3923,9 +4226,9 @@
         <v>43</v>
       </c>
     </row>
-    <row r="23" spans="1:23" ht="170.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="33">
-        <v>88</v>
+    <row r="23" spans="1:23" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="57">
+        <v>85</v>
       </c>
       <c r="B23" s="33" t="s">
         <v>34</v>
@@ -3934,22 +4237,22 @@
         <v>38</v>
       </c>
       <c r="D23" s="33" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E23" s="40" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="F23" s="34">
-        <v>45941</v>
+        <v>46140</v>
       </c>
       <c r="G23" s="34" t="s">
-        <v>158</v>
+        <v>198</v>
       </c>
       <c r="H23" s="34" t="s">
-        <v>176</v>
+        <v>218</v>
       </c>
       <c r="I23" s="39" t="s">
-        <v>194</v>
+        <v>238</v>
       </c>
       <c r="J23" s="35" t="s">
         <v>47</v>
@@ -3984,9 +4287,9 @@
         <v>43</v>
       </c>
     </row>
-    <row r="24" spans="1:23" ht="170.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="33">
-        <v>89</v>
+    <row r="24" spans="1:23" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="57">
+        <v>86</v>
       </c>
       <c r="B24" s="33" t="s">
         <v>34</v>
@@ -3995,22 +4298,22 @@
         <v>38</v>
       </c>
       <c r="D24" s="33" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="E24" s="40" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="F24" s="34">
-        <v>45941</v>
+        <v>46140</v>
       </c>
       <c r="G24" s="34" t="s">
-        <v>159</v>
+        <v>199</v>
       </c>
       <c r="H24" s="34" t="s">
-        <v>177</v>
+        <v>219</v>
       </c>
       <c r="I24" s="39" t="s">
-        <v>195</v>
+        <v>239</v>
       </c>
       <c r="J24" s="35" t="s">
         <v>47</v>
@@ -4045,9 +4348,9 @@
         <v>43</v>
       </c>
     </row>
-    <row r="25" spans="1:23" ht="170.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="33">
-        <v>90</v>
+    <row r="25" spans="1:23" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="57">
+        <v>87</v>
       </c>
       <c r="B25" s="33" t="s">
         <v>34</v>
@@ -4056,22 +4359,22 @@
         <v>38</v>
       </c>
       <c r="D25" s="33" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="E25" s="40" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="F25" s="34">
-        <v>45941</v>
+        <v>46140</v>
       </c>
       <c r="G25" s="34" t="s">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="H25" s="34" t="s">
-        <v>178</v>
+        <v>220</v>
       </c>
       <c r="I25" s="39" t="s">
-        <v>196</v>
+        <v>240</v>
       </c>
       <c r="J25" s="35" t="s">
         <v>47</v>
@@ -4106,9 +4409,9 @@
         <v>43</v>
       </c>
     </row>
-    <row r="26" spans="1:23" ht="170.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="33">
-        <v>91</v>
+    <row r="26" spans="1:23" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="57">
+        <v>88</v>
       </c>
       <c r="B26" s="33" t="s">
         <v>34</v>
@@ -4117,22 +4420,22 @@
         <v>38</v>
       </c>
       <c r="D26" s="33" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="E26" s="40" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="F26" s="34">
-        <v>45941</v>
+        <v>46140</v>
       </c>
       <c r="G26" s="34" t="s">
-        <v>161</v>
+        <v>201</v>
       </c>
       <c r="H26" s="34" t="s">
-        <v>179</v>
+        <v>221</v>
       </c>
       <c r="I26" s="39" t="s">
-        <v>197</v>
+        <v>241</v>
       </c>
       <c r="J26" s="35" t="s">
         <v>47</v>
@@ -4167,9 +4470,9 @@
         <v>43</v>
       </c>
     </row>
-    <row r="27" spans="1:23" ht="170.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="33">
-        <v>92</v>
+    <row r="27" spans="1:23" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="57">
+        <v>89</v>
       </c>
       <c r="B27" s="33" t="s">
         <v>34</v>
@@ -4178,22 +4481,22 @@
         <v>38</v>
       </c>
       <c r="D27" s="33" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="E27" s="40" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="F27" s="34">
-        <v>45941</v>
+        <v>46140</v>
       </c>
       <c r="G27" s="34" t="s">
-        <v>162</v>
+        <v>202</v>
       </c>
       <c r="H27" s="34" t="s">
-        <v>180</v>
+        <v>222</v>
       </c>
       <c r="I27" s="39" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="J27" s="35" t="s">
         <v>47</v>
@@ -4228,9 +4531,9 @@
         <v>43</v>
       </c>
     </row>
-    <row r="28" spans="1:23" ht="170.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="33">
-        <v>93</v>
+    <row r="28" spans="1:23" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="57">
+        <v>90</v>
       </c>
       <c r="B28" s="33" t="s">
         <v>34</v>
@@ -4239,22 +4542,22 @@
         <v>38</v>
       </c>
       <c r="D28" s="33" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="E28" s="40" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="F28" s="34">
-        <v>45941</v>
+        <v>46140</v>
       </c>
       <c r="G28" s="34" t="s">
-        <v>163</v>
+        <v>203</v>
       </c>
       <c r="H28" s="34" t="s">
-        <v>181</v>
+        <v>223</v>
       </c>
       <c r="I28" s="39" t="s">
-        <v>199</v>
+        <v>243</v>
       </c>
       <c r="J28" s="35" t="s">
         <v>47</v>
@@ -4289,9 +4592,9 @@
         <v>43</v>
       </c>
     </row>
-    <row r="29" spans="1:23" ht="170.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="33">
-        <v>462</v>
+    <row r="29" spans="1:23" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="57">
+        <v>91</v>
       </c>
       <c r="B29" s="33" t="s">
         <v>34</v>
@@ -4300,22 +4603,22 @@
         <v>38</v>
       </c>
       <c r="D29" s="33" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E29" s="40" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="F29" s="34">
-        <v>45941</v>
-      </c>
-      <c r="G29" s="33" t="s">
-        <v>164</v>
-      </c>
-      <c r="H29" s="33" t="s">
-        <v>182</v>
-      </c>
-      <c r="I29" s="41" t="s">
-        <v>200</v>
+        <v>46140</v>
+      </c>
+      <c r="G29" s="34" t="s">
+        <v>204</v>
+      </c>
+      <c r="H29" s="34" t="s">
+        <v>224</v>
+      </c>
+      <c r="I29" s="39" t="s">
+        <v>244</v>
       </c>
       <c r="J29" s="35" t="s">
         <v>47</v>
@@ -4344,15 +4647,15 @@
         <v>97</v>
       </c>
       <c r="T29" s="35"/>
-      <c r="U29" s="33"/>
-      <c r="V29" s="33"/>
-      <c r="W29" s="33" t="s">
+      <c r="U29" s="36"/>
+      <c r="V29" s="37"/>
+      <c r="W29" s="35" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="30" spans="1:23" ht="170.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="33">
-        <v>471</v>
+    <row r="30" spans="1:23" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="57">
+        <v>92</v>
       </c>
       <c r="B30" s="33" t="s">
         <v>34</v>
@@ -4361,45 +4664,59 @@
         <v>38</v>
       </c>
       <c r="D30" s="33" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="E30" s="40" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F30" s="34">
-        <v>45948</v>
+        <v>46140</v>
       </c>
       <c r="G30" s="34" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="H30" s="34" t="s">
-        <v>203</v>
+        <v>225</v>
       </c>
       <c r="I30" s="39" t="s">
-        <v>204</v>
+        <v>245</v>
       </c>
       <c r="J30" s="35" t="s">
         <v>47</v>
       </c>
       <c r="K30" s="35"/>
       <c r="L30" s="35"/>
-      <c r="M30" s="35"/>
-      <c r="N30" s="35"/>
-      <c r="O30" s="35"/>
-      <c r="P30" s="35"/>
-      <c r="Q30" s="35"/>
-      <c r="R30" s="35"/>
-      <c r="S30" s="35"/>
+      <c r="M30" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="N30" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="O30" s="35" t="s">
+        <v>147</v>
+      </c>
+      <c r="P30" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q30" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="R30" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="S30" s="35" t="s">
+        <v>97</v>
+      </c>
       <c r="T30" s="35"/>
       <c r="U30" s="36"/>
       <c r="V30" s="37"/>
       <c r="W30" s="35" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="31" spans="1:23" ht="170.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="33">
-        <v>472</v>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="57">
+        <v>93</v>
       </c>
       <c r="B31" s="33" t="s">
         <v>34</v>
@@ -4408,74 +4725,88 @@
         <v>38</v>
       </c>
       <c r="D31" s="33" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="E31" s="40" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="F31" s="34">
-        <v>45974</v>
+        <v>46140</v>
       </c>
       <c r="G31" s="34" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H31" s="34" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="I31" s="39" t="s">
-        <v>207</v>
+        <v>246</v>
       </c>
       <c r="J31" s="35" t="s">
         <v>47</v>
       </c>
       <c r="K31" s="35"/>
       <c r="L31" s="35"/>
-      <c r="M31" s="35"/>
-      <c r="N31" s="35"/>
-      <c r="O31" s="35"/>
-      <c r="P31" s="35"/>
-      <c r="Q31" s="35"/>
-      <c r="R31" s="35"/>
-      <c r="S31" s="35"/>
+      <c r="M31" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="N31" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="O31" s="35" t="s">
+        <v>147</v>
+      </c>
+      <c r="P31" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q31" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="R31" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="S31" s="35" t="s">
+        <v>97</v>
+      </c>
       <c r="T31" s="35"/>
       <c r="U31" s="36"/>
       <c r="V31" s="37"/>
       <c r="W31" s="35" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="32" spans="1:23" ht="170.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="33">
-        <v>474</v>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="32" spans="1:23" ht="120.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="57">
+        <v>152</v>
       </c>
       <c r="B32" s="33" t="s">
         <v>34</v>
       </c>
       <c r="C32" s="38" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="D32" s="33" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="E32" s="40" t="s">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="F32" s="34">
-        <v>45941</v>
+        <v>46140</v>
       </c>
       <c r="G32" s="34" t="s">
-        <v>165</v>
+        <v>251</v>
       </c>
       <c r="H32" s="34" t="s">
-        <v>183</v>
+        <v>271</v>
       </c>
       <c r="I32" s="39" t="s">
-        <v>201</v>
+        <v>291</v>
       </c>
       <c r="J32" s="35" t="s">
         <v>47</v>
       </c>
-      <c r="K32" s="35"/>
+      <c r="K32" s="44"/>
       <c r="L32" s="35"/>
       <c r="M32" s="35" t="s">
         <v>56</v>
@@ -4492,480 +4823,1267 @@
       <c r="Q32" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="R32" s="35" t="s">
-        <v>47</v>
-      </c>
-      <c r="S32" s="35" t="s">
-        <v>97</v>
-      </c>
+      <c r="R32" s="35"/>
+      <c r="S32" s="35"/>
       <c r="T32" s="35"/>
       <c r="U32" s="36"/>
       <c r="V32" s="37"/>
-      <c r="W32" s="35" t="s">
+      <c r="W32" s="35"/>
+    </row>
+    <row r="33" spans="1:23" ht="120.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="57">
+        <v>154</v>
+      </c>
+      <c r="B33" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="C33" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="D33" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="E33" s="40" t="s">
+        <v>171</v>
+      </c>
+      <c r="F33" s="34">
+        <v>46140</v>
+      </c>
+      <c r="G33" s="34" t="s">
+        <v>252</v>
+      </c>
+      <c r="H33" s="34" t="s">
+        <v>272</v>
+      </c>
+      <c r="I33" s="39" t="s">
+        <v>292</v>
+      </c>
+      <c r="J33" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="K33" s="44"/>
+      <c r="L33" s="35"/>
+      <c r="M33" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="N33" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="O33" s="35" t="s">
+        <v>147</v>
+      </c>
+      <c r="P33" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q33" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="R33" s="35"/>
+      <c r="S33" s="35"/>
+      <c r="T33" s="35"/>
+      <c r="U33" s="36"/>
+      <c r="V33" s="37"/>
+      <c r="W33" s="35"/>
+    </row>
+    <row r="34" spans="1:23" ht="120.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="57">
+        <v>155</v>
+      </c>
+      <c r="B34" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="C34" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="D34" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="E34" s="40" t="s">
+        <v>172</v>
+      </c>
+      <c r="F34" s="34">
+        <v>46140</v>
+      </c>
+      <c r="G34" s="34" t="s">
+        <v>253</v>
+      </c>
+      <c r="H34" s="34" t="s">
+        <v>273</v>
+      </c>
+      <c r="I34" s="39" t="s">
+        <v>293</v>
+      </c>
+      <c r="J34" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="K34" s="44"/>
+      <c r="L34" s="35"/>
+      <c r="M34" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="N34" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="O34" s="35" t="s">
+        <v>147</v>
+      </c>
+      <c r="P34" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q34" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="R34" s="35"/>
+      <c r="S34" s="35"/>
+      <c r="T34" s="35"/>
+      <c r="U34" s="36"/>
+      <c r="V34" s="37"/>
+      <c r="W34" s="35"/>
+    </row>
+    <row r="35" spans="1:23" ht="120.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="57">
+        <v>156</v>
+      </c>
+      <c r="B35" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="C35" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="D35" s="33" t="s">
+        <v>154</v>
+      </c>
+      <c r="E35" s="40" t="s">
+        <v>173</v>
+      </c>
+      <c r="F35" s="34">
+        <v>46140</v>
+      </c>
+      <c r="G35" s="34" t="s">
+        <v>254</v>
+      </c>
+      <c r="H35" s="34" t="s">
+        <v>274</v>
+      </c>
+      <c r="I35" s="39" t="s">
+        <v>294</v>
+      </c>
+      <c r="J35" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="K35" s="44"/>
+      <c r="L35" s="35"/>
+      <c r="M35" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="N35" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="O35" s="35" t="s">
+        <v>147</v>
+      </c>
+      <c r="P35" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q35" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="R35" s="35"/>
+      <c r="S35" s="35"/>
+      <c r="T35" s="35"/>
+      <c r="U35" s="36"/>
+      <c r="V35" s="37"/>
+      <c r="W35" s="35"/>
+    </row>
+    <row r="36" spans="1:23" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="57">
+        <v>159</v>
+      </c>
+      <c r="B36" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="C36" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="D36" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="E36" s="40" t="s">
+        <v>174</v>
+      </c>
+      <c r="F36" s="34">
+        <v>46140</v>
+      </c>
+      <c r="G36" s="34" t="s">
+        <v>255</v>
+      </c>
+      <c r="H36" s="34" t="s">
+        <v>275</v>
+      </c>
+      <c r="I36" s="39" t="s">
+        <v>295</v>
+      </c>
+      <c r="J36" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="K36" s="35"/>
+      <c r="L36" s="35"/>
+      <c r="M36" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="N36" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="O36" s="35" t="s">
+        <v>147</v>
+      </c>
+      <c r="P36" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q36" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="R36" s="35"/>
+      <c r="S36" s="35"/>
+      <c r="T36" s="35"/>
+      <c r="U36" s="36"/>
+      <c r="V36" s="37"/>
+      <c r="W36" s="35"/>
+    </row>
+    <row r="37" spans="1:23" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="57">
+        <v>160</v>
+      </c>
+      <c r="B37" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="C37" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="D37" s="33" t="s">
+        <v>156</v>
+      </c>
+      <c r="E37" s="40" t="s">
+        <v>175</v>
+      </c>
+      <c r="F37" s="34">
+        <v>46140</v>
+      </c>
+      <c r="G37" s="34" t="s">
+        <v>256</v>
+      </c>
+      <c r="H37" s="34" t="s">
+        <v>276</v>
+      </c>
+      <c r="I37" s="39" t="s">
+        <v>296</v>
+      </c>
+      <c r="J37" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="K37" s="35"/>
+      <c r="L37" s="35"/>
+      <c r="M37" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="N37" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="O37" s="35" t="s">
+        <v>147</v>
+      </c>
+      <c r="P37" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q37" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="R37" s="35"/>
+      <c r="S37" s="35"/>
+      <c r="T37" s="35"/>
+      <c r="U37" s="36"/>
+      <c r="V37" s="37"/>
+      <c r="W37" s="35"/>
+    </row>
+    <row r="38" spans="1:23" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="57">
+        <v>161</v>
+      </c>
+      <c r="B38" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="C38" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="D38" s="33" t="s">
+        <v>157</v>
+      </c>
+      <c r="E38" s="40" t="s">
+        <v>176</v>
+      </c>
+      <c r="F38" s="34">
+        <v>46140</v>
+      </c>
+      <c r="G38" s="34" t="s">
+        <v>257</v>
+      </c>
+      <c r="H38" s="34" t="s">
+        <v>277</v>
+      </c>
+      <c r="I38" s="39" t="s">
+        <v>297</v>
+      </c>
+      <c r="J38" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="K38" s="35"/>
+      <c r="L38" s="35"/>
+      <c r="M38" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="N38" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="O38" s="35" t="s">
+        <v>147</v>
+      </c>
+      <c r="P38" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q38" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="R38" s="35"/>
+      <c r="S38" s="35"/>
+      <c r="T38" s="35"/>
+      <c r="U38" s="36"/>
+      <c r="V38" s="37"/>
+      <c r="W38" s="35"/>
+    </row>
+    <row r="39" spans="1:23" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="57">
+        <v>162</v>
+      </c>
+      <c r="B39" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="C39" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="D39" s="33" t="s">
+        <v>158</v>
+      </c>
+      <c r="E39" s="40" t="s">
+        <v>177</v>
+      </c>
+      <c r="F39" s="34">
+        <v>46140</v>
+      </c>
+      <c r="G39" s="34" t="s">
+        <v>258</v>
+      </c>
+      <c r="H39" s="34" t="s">
+        <v>278</v>
+      </c>
+      <c r="I39" s="39" t="s">
+        <v>298</v>
+      </c>
+      <c r="J39" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="K39" s="44"/>
+      <c r="L39" s="35"/>
+      <c r="M39" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="N39" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="O39" s="35" t="s">
+        <v>147</v>
+      </c>
+      <c r="P39" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q39" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="R39" s="35"/>
+      <c r="S39" s="35"/>
+      <c r="T39" s="35"/>
+      <c r="U39" s="36"/>
+      <c r="V39" s="37"/>
+      <c r="W39" s="35"/>
+    </row>
+    <row r="40" spans="1:23" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="57">
+        <v>163</v>
+      </c>
+      <c r="B40" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="C40" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="D40" s="33" t="s">
+        <v>159</v>
+      </c>
+      <c r="E40" s="40" t="s">
+        <v>178</v>
+      </c>
+      <c r="F40" s="34">
+        <v>46140</v>
+      </c>
+      <c r="G40" s="34" t="s">
+        <v>259</v>
+      </c>
+      <c r="H40" s="34" t="s">
+        <v>279</v>
+      </c>
+      <c r="I40" s="39" t="s">
+        <v>299</v>
+      </c>
+      <c r="J40" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="K40" s="44"/>
+      <c r="L40" s="35"/>
+      <c r="M40" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="N40" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="O40" s="35" t="s">
+        <v>147</v>
+      </c>
+      <c r="P40" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q40" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="R40" s="35"/>
+      <c r="S40" s="35"/>
+      <c r="T40" s="35"/>
+      <c r="U40" s="36"/>
+      <c r="V40" s="37"/>
+      <c r="W40" s="35"/>
+    </row>
+    <row r="41" spans="1:23" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="57">
+        <v>164</v>
+      </c>
+      <c r="B41" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="C41" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="D41" s="33" t="s">
+        <v>160</v>
+      </c>
+      <c r="E41" s="40" t="s">
+        <v>179</v>
+      </c>
+      <c r="F41" s="34">
+        <v>46140</v>
+      </c>
+      <c r="G41" s="34" t="s">
+        <v>260</v>
+      </c>
+      <c r="H41" s="34" t="s">
+        <v>280</v>
+      </c>
+      <c r="I41" s="39" t="s">
+        <v>300</v>
+      </c>
+      <c r="J41" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="K41" s="44"/>
+      <c r="L41" s="35"/>
+      <c r="M41" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="N41" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="O41" s="35" t="s">
+        <v>147</v>
+      </c>
+      <c r="P41" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q41" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="R41" s="35"/>
+      <c r="S41" s="35"/>
+      <c r="T41" s="35"/>
+      <c r="U41" s="36"/>
+      <c r="V41" s="37"/>
+      <c r="W41" s="35"/>
+    </row>
+    <row r="42" spans="1:23" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="57">
+        <v>165</v>
+      </c>
+      <c r="B42" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="C42" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="D42" s="33" t="s">
+        <v>161</v>
+      </c>
+      <c r="E42" s="40" t="s">
+        <v>180</v>
+      </c>
+      <c r="F42" s="34">
+        <v>46140</v>
+      </c>
+      <c r="G42" s="34" t="s">
+        <v>261</v>
+      </c>
+      <c r="H42" s="34" t="s">
+        <v>281</v>
+      </c>
+      <c r="I42" s="39" t="s">
+        <v>301</v>
+      </c>
+      <c r="J42" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="K42" s="44"/>
+      <c r="L42" s="35"/>
+      <c r="M42" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="N42" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="O42" s="35" t="s">
+        <v>147</v>
+      </c>
+      <c r="P42" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q42" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="R42" s="35"/>
+      <c r="S42" s="35"/>
+      <c r="T42" s="35"/>
+      <c r="U42" s="36"/>
+      <c r="V42" s="37"/>
+      <c r="W42" s="35"/>
+    </row>
+    <row r="43" spans="1:23" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="57">
+        <v>166</v>
+      </c>
+      <c r="B43" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="C43" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="D43" s="33" t="s">
+        <v>162</v>
+      </c>
+      <c r="E43" s="40" t="s">
+        <v>181</v>
+      </c>
+      <c r="F43" s="34">
+        <v>46140</v>
+      </c>
+      <c r="G43" s="34" t="s">
+        <v>262</v>
+      </c>
+      <c r="H43" s="34" t="s">
+        <v>282</v>
+      </c>
+      <c r="I43" s="39" t="s">
+        <v>302</v>
+      </c>
+      <c r="J43" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="K43" s="44"/>
+      <c r="L43" s="35"/>
+      <c r="M43" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="N43" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="O43" s="35" t="s">
+        <v>147</v>
+      </c>
+      <c r="P43" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q43" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="R43" s="35"/>
+      <c r="S43" s="35"/>
+      <c r="T43" s="35"/>
+      <c r="U43" s="36"/>
+      <c r="V43" s="37"/>
+      <c r="W43" s="35"/>
+    </row>
+    <row r="44" spans="1:23" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="57">
+        <v>167</v>
+      </c>
+      <c r="B44" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="C44" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="D44" s="33" t="s">
+        <v>163</v>
+      </c>
+      <c r="E44" s="40" t="s">
+        <v>182</v>
+      </c>
+      <c r="F44" s="34">
+        <v>46140</v>
+      </c>
+      <c r="G44" s="34" t="s">
+        <v>263</v>
+      </c>
+      <c r="H44" s="34" t="s">
+        <v>283</v>
+      </c>
+      <c r="I44" s="39" t="s">
+        <v>303</v>
+      </c>
+      <c r="J44" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="K44" s="44"/>
+      <c r="L44" s="35"/>
+      <c r="M44" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="N44" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="O44" s="35" t="s">
+        <v>147</v>
+      </c>
+      <c r="P44" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q44" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="R44" s="35"/>
+      <c r="S44" s="35"/>
+      <c r="T44" s="35"/>
+      <c r="U44" s="36"/>
+      <c r="V44" s="37"/>
+      <c r="W44" s="35"/>
+    </row>
+    <row r="45" spans="1:23" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="57">
+        <v>168</v>
+      </c>
+      <c r="B45" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="C45" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="D45" s="33" t="s">
+        <v>164</v>
+      </c>
+      <c r="E45" s="40" t="s">
+        <v>183</v>
+      </c>
+      <c r="F45" s="34">
+        <v>46140</v>
+      </c>
+      <c r="G45" s="34" t="s">
+        <v>264</v>
+      </c>
+      <c r="H45" s="34" t="s">
+        <v>284</v>
+      </c>
+      <c r="I45" s="39" t="s">
+        <v>304</v>
+      </c>
+      <c r="J45" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="K45" s="44"/>
+      <c r="L45" s="35"/>
+      <c r="M45" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="N45" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="O45" s="35" t="s">
+        <v>147</v>
+      </c>
+      <c r="P45" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q45" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="R45" s="35"/>
+      <c r="S45" s="35"/>
+      <c r="T45" s="35"/>
+      <c r="U45" s="36"/>
+      <c r="V45" s="37"/>
+      <c r="W45" s="35"/>
+    </row>
+    <row r="46" spans="1:23" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="57">
+        <v>169</v>
+      </c>
+      <c r="B46" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="C46" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="D46" s="33" t="s">
+        <v>165</v>
+      </c>
+      <c r="E46" s="40" t="s">
+        <v>184</v>
+      </c>
+      <c r="F46" s="34">
+        <v>46140</v>
+      </c>
+      <c r="G46" s="34" t="s">
+        <v>265</v>
+      </c>
+      <c r="H46" s="34" t="s">
+        <v>285</v>
+      </c>
+      <c r="I46" s="39" t="s">
+        <v>305</v>
+      </c>
+      <c r="J46" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="K46" s="44"/>
+      <c r="L46" s="35"/>
+      <c r="M46" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="N46" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="O46" s="35" t="s">
+        <v>147</v>
+      </c>
+      <c r="P46" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q46" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="R46" s="35"/>
+      <c r="S46" s="35"/>
+      <c r="T46" s="35"/>
+      <c r="U46" s="36"/>
+      <c r="V46" s="37"/>
+      <c r="W46" s="35"/>
+    </row>
+    <row r="47" spans="1:23" ht="135.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="57">
+        <v>448</v>
+      </c>
+      <c r="B47" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="C47" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="D47" s="33" t="s">
+        <v>166</v>
+      </c>
+      <c r="E47" s="40" t="s">
+        <v>185</v>
+      </c>
+      <c r="F47" s="34">
+        <v>46140</v>
+      </c>
+      <c r="G47" s="34" t="s">
+        <v>266</v>
+      </c>
+      <c r="H47" s="34" t="s">
+        <v>286</v>
+      </c>
+      <c r="I47" s="39" t="s">
+        <v>306</v>
+      </c>
+      <c r="J47" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="K47" s="44"/>
+      <c r="L47" s="35"/>
+      <c r="M47" s="35"/>
+      <c r="N47" s="35"/>
+      <c r="O47" s="35"/>
+      <c r="P47" s="35"/>
+      <c r="Q47" s="35"/>
+      <c r="R47" s="35"/>
+      <c r="S47" s="35"/>
+      <c r="T47" s="35"/>
+      <c r="U47" s="36"/>
+      <c r="V47" s="37"/>
+      <c r="W47" s="35"/>
+    </row>
+    <row r="48" spans="1:23" ht="135.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="57">
+        <v>449</v>
+      </c>
+      <c r="B48" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="C48" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="D48" s="33" t="s">
+        <v>167</v>
+      </c>
+      <c r="E48" s="40" t="s">
+        <v>186</v>
+      </c>
+      <c r="F48" s="34">
+        <v>46140</v>
+      </c>
+      <c r="G48" s="34" t="s">
+        <v>267</v>
+      </c>
+      <c r="H48" s="34" t="s">
+        <v>287</v>
+      </c>
+      <c r="I48" s="39" t="s">
+        <v>307</v>
+      </c>
+      <c r="J48" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="K48" s="35"/>
+      <c r="L48" s="35"/>
+      <c r="M48" s="35"/>
+      <c r="N48" s="35"/>
+      <c r="O48" s="35"/>
+      <c r="P48" s="35"/>
+      <c r="Q48" s="35"/>
+      <c r="R48" s="35"/>
+      <c r="S48" s="35"/>
+      <c r="T48" s="35"/>
+      <c r="U48" s="36"/>
+      <c r="V48" s="37"/>
+      <c r="W48" s="35"/>
+    </row>
+    <row r="49" spans="1:23" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="57">
+        <v>461</v>
+      </c>
+      <c r="B49" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="C49" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="D49" s="33" t="s">
+        <v>168</v>
+      </c>
+      <c r="E49" s="40" t="s">
+        <v>187</v>
+      </c>
+      <c r="F49" s="34">
+        <v>46140</v>
+      </c>
+      <c r="G49" s="33" t="s">
+        <v>268</v>
+      </c>
+      <c r="H49" s="33" t="s">
+        <v>288</v>
+      </c>
+      <c r="I49" s="41" t="s">
+        <v>308</v>
+      </c>
+      <c r="J49" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="K49" s="35"/>
+      <c r="L49" s="35"/>
+      <c r="M49" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="N49" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="O49" s="35" t="s">
+        <v>147</v>
+      </c>
+      <c r="P49" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q49" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="R49" s="35"/>
+      <c r="S49" s="35"/>
+      <c r="T49" s="35"/>
+      <c r="U49" s="33"/>
+      <c r="V49" s="33"/>
+      <c r="W49" s="35"/>
+    </row>
+    <row r="50" spans="1:23" ht="120.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="57">
+        <v>462</v>
+      </c>
+      <c r="B50" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="C50" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="D50" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="E50" s="40" t="s">
+        <v>131</v>
+      </c>
+      <c r="F50" s="34">
+        <v>46140</v>
+      </c>
+      <c r="G50" s="33" t="s">
+        <v>207</v>
+      </c>
+      <c r="H50" s="33" t="s">
+        <v>227</v>
+      </c>
+      <c r="I50" s="41" t="s">
+        <v>247</v>
+      </c>
+      <c r="J50" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="K50" s="35"/>
+      <c r="L50" s="35"/>
+      <c r="M50" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="N50" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="O50" s="35" t="s">
+        <v>147</v>
+      </c>
+      <c r="P50" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q50" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="R50" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="S50" s="35" t="s">
+        <v>97</v>
+      </c>
+      <c r="T50" s="35"/>
+      <c r="U50" s="33"/>
+      <c r="V50" s="33"/>
+      <c r="W50" s="35" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="33" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="6"/>
-      <c r="I33" s="6"/>
-      <c r="J33" s="7"/>
-      <c r="K33" s="7"/>
-      <c r="L33" s="7"/>
-      <c r="M33" s="7"/>
-      <c r="N33" s="7"/>
-      <c r="O33" s="7"/>
-      <c r="P33" s="7"/>
-      <c r="Q33" s="7"/>
-      <c r="R33" s="7"/>
-      <c r="S33" s="7"/>
-      <c r="T33" s="7"/>
-      <c r="U33" s="8"/>
-      <c r="V33" s="2"/>
-      <c r="W33" s="9"/>
-    </row>
-    <row r="34" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F34" s="6"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="6"/>
-      <c r="I34" s="6"/>
-      <c r="J34" s="7"/>
-      <c r="K34" s="7"/>
-      <c r="L34" s="7"/>
-      <c r="M34" s="7"/>
-      <c r="N34" s="7"/>
-      <c r="O34" s="7"/>
-      <c r="P34" s="7"/>
-      <c r="Q34" s="7"/>
-      <c r="R34" s="7"/>
-      <c r="S34" s="7"/>
-      <c r="T34" s="7"/>
-      <c r="U34" s="8"/>
-      <c r="V34" s="2"/>
-      <c r="W34" s="9"/>
-    </row>
-    <row r="35" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F35" s="6"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="6"/>
-      <c r="I35" s="6"/>
-      <c r="J35" s="7"/>
-      <c r="K35" s="7"/>
-      <c r="L35" s="7"/>
-      <c r="M35" s="7"/>
-      <c r="N35" s="7"/>
-      <c r="O35" s="7"/>
-      <c r="P35" s="7"/>
-      <c r="Q35" s="7"/>
-      <c r="R35" s="7"/>
-      <c r="S35" s="7"/>
-      <c r="T35" s="7"/>
-      <c r="U35" s="8"/>
-      <c r="V35" s="2"/>
-      <c r="W35" s="9"/>
-    </row>
-    <row r="36" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F36" s="6"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="6"/>
-      <c r="I36" s="6"/>
-      <c r="J36" s="7"/>
-      <c r="K36" s="7"/>
-      <c r="L36" s="7"/>
-      <c r="M36" s="7"/>
-      <c r="N36" s="7"/>
-      <c r="O36" s="7"/>
-      <c r="P36" s="7"/>
-      <c r="Q36" s="7"/>
-      <c r="R36" s="7"/>
-      <c r="S36" s="7"/>
-      <c r="T36" s="7"/>
-      <c r="U36" s="8"/>
-      <c r="V36" s="2"/>
-      <c r="W36" s="9"/>
-    </row>
-    <row r="37" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F37" s="6"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="6"/>
-      <c r="I37" s="6"/>
-      <c r="J37" s="7"/>
-      <c r="K37" s="7"/>
-      <c r="L37" s="7"/>
-      <c r="M37" s="7"/>
-      <c r="N37" s="7"/>
-      <c r="O37" s="7"/>
-      <c r="P37" s="7"/>
-      <c r="Q37" s="7"/>
-      <c r="R37" s="7"/>
-      <c r="S37" s="7"/>
-      <c r="T37" s="7"/>
-      <c r="U37" s="8"/>
-      <c r="V37" s="2"/>
-      <c r="W37" s="9"/>
-    </row>
-    <row r="38" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F38" s="6"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="6"/>
-      <c r="I38" s="6"/>
-      <c r="J38" s="7"/>
-      <c r="K38" s="7"/>
-      <c r="L38" s="7"/>
-      <c r="M38" s="7"/>
-      <c r="N38" s="7"/>
-      <c r="O38" s="7"/>
-      <c r="P38" s="7"/>
-      <c r="Q38" s="7"/>
-      <c r="R38" s="7"/>
-      <c r="S38" s="7"/>
-      <c r="T38" s="7"/>
-      <c r="U38" s="8"/>
-      <c r="V38" s="2"/>
-      <c r="W38" s="9"/>
-    </row>
-    <row r="39" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F39" s="6"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="6"/>
-      <c r="I39" s="6"/>
-      <c r="J39" s="7"/>
-      <c r="K39" s="7"/>
-      <c r="L39" s="7"/>
-      <c r="M39" s="7"/>
-      <c r="N39" s="7"/>
-      <c r="O39" s="7"/>
-      <c r="P39" s="7"/>
-      <c r="Q39" s="7"/>
-      <c r="R39" s="7"/>
-      <c r="S39" s="7"/>
-      <c r="T39" s="7"/>
-      <c r="U39" s="8"/>
-      <c r="V39" s="2"/>
-      <c r="W39" s="9"/>
-    </row>
-    <row r="40" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F40" s="6"/>
-      <c r="G40" s="6"/>
-      <c r="H40" s="6"/>
-      <c r="I40" s="6"/>
-      <c r="J40" s="7"/>
-      <c r="K40" s="7"/>
-      <c r="L40" s="7"/>
-      <c r="M40" s="7"/>
-      <c r="N40" s="7"/>
-      <c r="O40" s="7"/>
-      <c r="P40" s="7"/>
-      <c r="Q40" s="7"/>
-      <c r="R40" s="7"/>
-      <c r="S40" s="7"/>
-      <c r="T40" s="7"/>
-      <c r="U40" s="8"/>
-      <c r="V40" s="2"/>
-      <c r="W40" s="9"/>
-    </row>
-    <row r="41" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F41" s="6"/>
-      <c r="G41" s="6"/>
-      <c r="H41" s="6"/>
-      <c r="I41" s="6"/>
-      <c r="J41" s="7"/>
-      <c r="K41" s="7"/>
-      <c r="L41" s="7"/>
-      <c r="M41" s="7"/>
-      <c r="N41" s="7"/>
-      <c r="O41" s="7"/>
-      <c r="P41" s="7"/>
-      <c r="Q41" s="7"/>
-      <c r="R41" s="7"/>
-      <c r="S41" s="7"/>
-      <c r="T41" s="7"/>
-      <c r="U41" s="8"/>
-      <c r="V41" s="2"/>
-      <c r="W41" s="9"/>
-    </row>
-    <row r="42" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F42" s="6"/>
-      <c r="G42" s="6"/>
-      <c r="H42" s="6"/>
-      <c r="I42" s="6"/>
-      <c r="J42" s="7"/>
-      <c r="K42" s="7"/>
-      <c r="L42" s="7"/>
-      <c r="M42" s="7"/>
-      <c r="N42" s="7"/>
-      <c r="O42" s="7"/>
-      <c r="P42" s="7"/>
-      <c r="Q42" s="7"/>
-      <c r="R42" s="7"/>
-      <c r="S42" s="7"/>
-      <c r="T42" s="7"/>
-      <c r="U42" s="8"/>
-      <c r="V42" s="2"/>
-      <c r="W42" s="9"/>
-    </row>
-    <row r="43" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F43" s="6"/>
-      <c r="G43" s="6"/>
-      <c r="H43" s="6"/>
-      <c r="I43" s="6"/>
-      <c r="J43" s="7"/>
-      <c r="K43" s="7"/>
-      <c r="L43" s="7"/>
-      <c r="M43" s="7"/>
-      <c r="N43" s="7"/>
-      <c r="O43" s="7"/>
-      <c r="P43" s="7"/>
-      <c r="Q43" s="7"/>
-      <c r="R43" s="7"/>
-      <c r="S43" s="7"/>
-      <c r="T43" s="7"/>
-      <c r="U43" s="8"/>
-      <c r="V43" s="2"/>
-      <c r="W43" s="9"/>
-    </row>
-    <row r="44" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F44" s="6"/>
-      <c r="G44" s="6"/>
-      <c r="H44" s="6"/>
-      <c r="I44" s="6"/>
-      <c r="J44" s="7"/>
-      <c r="K44" s="7"/>
-      <c r="L44" s="7"/>
-      <c r="M44" s="7"/>
-      <c r="N44" s="7"/>
-      <c r="O44" s="7"/>
-      <c r="P44" s="7"/>
-      <c r="Q44" s="7"/>
-      <c r="R44" s="7"/>
-      <c r="S44" s="7"/>
-      <c r="T44" s="7"/>
-      <c r="U44" s="8"/>
-      <c r="V44" s="2"/>
-      <c r="W44" s="9"/>
-    </row>
-    <row r="45" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F45" s="6"/>
-      <c r="G45" s="6"/>
-      <c r="H45" s="6"/>
-      <c r="I45" s="6"/>
-      <c r="J45" s="7"/>
-      <c r="K45" s="7"/>
-      <c r="L45" s="7"/>
-      <c r="M45" s="7"/>
-      <c r="N45" s="7"/>
-      <c r="O45" s="7"/>
-      <c r="P45" s="7"/>
-      <c r="Q45" s="7"/>
-      <c r="R45" s="7"/>
-      <c r="S45" s="7"/>
-      <c r="T45" s="7"/>
-      <c r="U45" s="8"/>
-      <c r="V45" s="2"/>
-      <c r="W45" s="9"/>
-    </row>
-    <row r="46" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F46" s="6"/>
-      <c r="G46" s="6"/>
-      <c r="H46" s="6"/>
-      <c r="I46" s="6"/>
-      <c r="J46" s="7"/>
-      <c r="K46" s="7"/>
-      <c r="L46" s="7"/>
-      <c r="M46" s="7"/>
-      <c r="N46" s="7"/>
-      <c r="O46" s="7"/>
-      <c r="P46" s="7"/>
-      <c r="Q46" s="7"/>
-      <c r="R46" s="7"/>
-      <c r="S46" s="7"/>
-      <c r="T46" s="7"/>
-      <c r="U46" s="8"/>
-      <c r="V46" s="2"/>
-      <c r="W46" s="9"/>
-    </row>
-    <row r="47" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F47" s="6"/>
-      <c r="G47" s="6"/>
-      <c r="H47" s="6"/>
-      <c r="I47" s="6"/>
-      <c r="J47" s="7"/>
-      <c r="K47" s="7"/>
-      <c r="L47" s="7"/>
-      <c r="M47" s="7"/>
-      <c r="N47" s="7"/>
-      <c r="O47" s="7"/>
-      <c r="P47" s="7"/>
-      <c r="Q47" s="7"/>
-      <c r="R47" s="7"/>
-      <c r="S47" s="7"/>
-      <c r="T47" s="7"/>
-      <c r="U47" s="8"/>
-      <c r="V47" s="2"/>
-      <c r="W47" s="9"/>
-    </row>
-    <row r="48" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F48" s="6"/>
-      <c r="G48" s="6"/>
-      <c r="H48" s="6"/>
-      <c r="I48" s="6"/>
-      <c r="J48" s="7"/>
-      <c r="K48" s="7"/>
-      <c r="L48" s="7"/>
-      <c r="M48" s="7"/>
-      <c r="N48" s="7"/>
-      <c r="O48" s="7"/>
-      <c r="P48" s="7"/>
-      <c r="Q48" s="7"/>
-      <c r="R48" s="7"/>
-      <c r="S48" s="7"/>
-      <c r="T48" s="7"/>
-      <c r="U48" s="8"/>
-      <c r="V48" s="2"/>
-      <c r="W48" s="9"/>
-    </row>
-    <row r="49" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F49" s="6"/>
-      <c r="G49" s="6"/>
-      <c r="H49" s="6"/>
-      <c r="I49" s="6"/>
-      <c r="J49" s="7"/>
-      <c r="K49" s="7"/>
-      <c r="L49" s="7"/>
-      <c r="M49" s="7"/>
-      <c r="N49" s="7"/>
-      <c r="O49" s="7"/>
-      <c r="P49" s="7"/>
-      <c r="Q49" s="7"/>
-      <c r="R49" s="7"/>
-      <c r="S49" s="7"/>
-      <c r="T49" s="7"/>
-      <c r="U49" s="8"/>
-      <c r="V49" s="2"/>
-      <c r="W49" s="9"/>
-    </row>
-    <row r="50" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F50" s="6"/>
-      <c r="G50" s="6"/>
-      <c r="H50" s="6"/>
-      <c r="I50" s="6"/>
-      <c r="J50" s="7"/>
-      <c r="K50" s="7"/>
-      <c r="L50" s="7"/>
-      <c r="M50" s="7"/>
-      <c r="N50" s="7"/>
-      <c r="O50" s="7"/>
-      <c r="P50" s="7"/>
-      <c r="Q50" s="7"/>
-      <c r="R50" s="7"/>
-      <c r="S50" s="7"/>
-      <c r="T50" s="7"/>
-      <c r="U50" s="8"/>
-      <c r="V50" s="2"/>
-      <c r="W50" s="9"/>
-    </row>
-    <row r="51" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F51" s="6"/>
-      <c r="G51" s="6"/>
-      <c r="H51" s="6"/>
-      <c r="I51" s="6"/>
-      <c r="J51" s="7"/>
-      <c r="K51" s="7"/>
-      <c r="L51" s="7"/>
-      <c r="M51" s="7"/>
-      <c r="N51" s="7"/>
-      <c r="O51" s="7"/>
-      <c r="P51" s="7"/>
-      <c r="Q51" s="7"/>
-      <c r="R51" s="7"/>
-      <c r="S51" s="7"/>
-      <c r="T51" s="7"/>
-      <c r="U51" s="8"/>
-      <c r="V51" s="2"/>
-      <c r="W51" s="9"/>
-    </row>
-    <row r="52" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F52" s="6"/>
-      <c r="G52" s="6"/>
-      <c r="H52" s="6"/>
-      <c r="I52" s="6"/>
-      <c r="J52" s="7"/>
-      <c r="K52" s="7"/>
-      <c r="L52" s="7"/>
-      <c r="M52" s="7"/>
-      <c r="N52" s="7"/>
-      <c r="O52" s="7"/>
-      <c r="P52" s="7"/>
-      <c r="Q52" s="7"/>
-      <c r="R52" s="7"/>
-      <c r="S52" s="7"/>
-      <c r="T52" s="7"/>
-      <c r="U52" s="8"/>
-      <c r="V52" s="2"/>
-      <c r="W52" s="9"/>
-    </row>
-    <row r="53" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F53" s="6"/>
-      <c r="G53" s="6"/>
-      <c r="H53" s="6"/>
-      <c r="I53" s="6"/>
-      <c r="J53" s="7"/>
-      <c r="K53" s="7"/>
-      <c r="L53" s="7"/>
-      <c r="M53" s="7"/>
-      <c r="N53" s="7"/>
-      <c r="O53" s="7"/>
-      <c r="P53" s="7"/>
-      <c r="Q53" s="7"/>
-      <c r="R53" s="7"/>
-      <c r="S53" s="7"/>
-      <c r="T53" s="7"/>
-      <c r="U53" s="8"/>
-      <c r="V53" s="2"/>
-      <c r="W53" s="9"/>
-    </row>
-    <row r="54" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F54" s="6"/>
-      <c r="G54" s="6"/>
-      <c r="H54" s="6"/>
-      <c r="I54" s="6"/>
-      <c r="J54" s="7"/>
-      <c r="K54" s="7"/>
-      <c r="L54" s="7"/>
-      <c r="M54" s="7"/>
-      <c r="N54" s="7"/>
-      <c r="O54" s="7"/>
-      <c r="P54" s="7"/>
-      <c r="Q54" s="7"/>
-      <c r="R54" s="7"/>
-      <c r="S54" s="7"/>
-      <c r="T54" s="7"/>
-      <c r="U54" s="8"/>
-      <c r="V54" s="2"/>
-      <c r="W54" s="9"/>
-    </row>
-    <row r="55" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F55" s="6"/>
-      <c r="G55" s="6"/>
-      <c r="H55" s="6"/>
-      <c r="I55" s="6"/>
-      <c r="J55" s="7"/>
-      <c r="K55" s="7"/>
-      <c r="L55" s="7"/>
-      <c r="M55" s="7"/>
-      <c r="N55" s="7"/>
-      <c r="O55" s="7"/>
-      <c r="P55" s="7"/>
-      <c r="Q55" s="7"/>
-      <c r="R55" s="7"/>
-      <c r="S55" s="7"/>
-      <c r="T55" s="7"/>
-      <c r="U55" s="8"/>
-      <c r="V55" s="2"/>
-      <c r="W55" s="9"/>
-    </row>
-    <row r="56" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:23" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="57">
+        <v>468</v>
+      </c>
+      <c r="B51" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="C51" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="D51" s="33" t="s">
+        <v>169</v>
+      </c>
+      <c r="E51" s="40" t="s">
+        <v>188</v>
+      </c>
+      <c r="F51" s="34">
+        <v>46140</v>
+      </c>
+      <c r="G51" s="33" t="s">
+        <v>269</v>
+      </c>
+      <c r="H51" s="33" t="s">
+        <v>289</v>
+      </c>
+      <c r="I51" s="41" t="s">
+        <v>309</v>
+      </c>
+      <c r="J51" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="K51" s="35"/>
+      <c r="L51" s="35"/>
+      <c r="M51" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="N51" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="O51" s="35" t="s">
+        <v>147</v>
+      </c>
+      <c r="P51" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q51" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="R51" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="S51" s="35" t="s">
+        <v>97</v>
+      </c>
+      <c r="T51" s="35"/>
+      <c r="U51" s="33"/>
+      <c r="V51" s="33"/>
+      <c r="W51" s="35" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="52" spans="1:23" ht="120.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="57">
+        <v>471</v>
+      </c>
+      <c r="B52" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="C52" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="D52" s="33" t="s">
+        <v>132</v>
+      </c>
+      <c r="E52" s="40" t="s">
+        <v>133</v>
+      </c>
+      <c r="F52" s="34">
+        <v>46140</v>
+      </c>
+      <c r="G52" s="34" t="s">
+        <v>208</v>
+      </c>
+      <c r="H52" s="34" t="s">
+        <v>228</v>
+      </c>
+      <c r="I52" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="J52" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="K52" s="35"/>
+      <c r="L52" s="35"/>
+      <c r="M52" s="35"/>
+      <c r="N52" s="35"/>
+      <c r="O52" s="35"/>
+      <c r="P52" s="35"/>
+      <c r="Q52" s="35"/>
+      <c r="R52" s="35"/>
+      <c r="S52" s="35"/>
+      <c r="T52" s="35"/>
+      <c r="U52" s="36"/>
+      <c r="V52" s="37"/>
+      <c r="W52" s="35" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="53" spans="1:23" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="57">
+        <v>472</v>
+      </c>
+      <c r="B53" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="C53" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="D53" s="33" t="s">
+        <v>134</v>
+      </c>
+      <c r="E53" s="40" t="s">
+        <v>135</v>
+      </c>
+      <c r="F53" s="34">
+        <v>46140</v>
+      </c>
+      <c r="G53" s="34" t="s">
+        <v>209</v>
+      </c>
+      <c r="H53" s="34" t="s">
+        <v>229</v>
+      </c>
+      <c r="I53" s="39" t="s">
+        <v>249</v>
+      </c>
+      <c r="J53" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="K53" s="35"/>
+      <c r="L53" s="35"/>
+      <c r="M53" s="35"/>
+      <c r="N53" s="35"/>
+      <c r="O53" s="35"/>
+      <c r="P53" s="35"/>
+      <c r="Q53" s="35"/>
+      <c r="R53" s="35"/>
+      <c r="S53" s="35"/>
+      <c r="T53" s="35"/>
+      <c r="U53" s="36"/>
+      <c r="V53" s="37"/>
+      <c r="W53" s="35" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="54" spans="1:23" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="57">
+        <v>474</v>
+      </c>
+      <c r="B54" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="C54" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="D54" s="33" t="s">
+        <v>139</v>
+      </c>
+      <c r="E54" s="40" t="s">
+        <v>140</v>
+      </c>
+      <c r="F54" s="34">
+        <v>46140</v>
+      </c>
+      <c r="G54" s="34" t="s">
+        <v>210</v>
+      </c>
+      <c r="H54" s="34" t="s">
+        <v>230</v>
+      </c>
+      <c r="I54" s="39" t="s">
+        <v>250</v>
+      </c>
+      <c r="J54" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="K54" s="35"/>
+      <c r="L54" s="35"/>
+      <c r="M54" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="N54" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="O54" s="35" t="s">
+        <v>147</v>
+      </c>
+      <c r="P54" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q54" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="R54" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="S54" s="35" t="s">
+        <v>97</v>
+      </c>
+      <c r="T54" s="35"/>
+      <c r="U54" s="36"/>
+      <c r="V54" s="37"/>
+      <c r="W54" s="35" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="55" spans="1:23" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="57">
+        <v>475</v>
+      </c>
+      <c r="B55" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="C55" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="D55" s="42" t="s">
+        <v>150</v>
+      </c>
+      <c r="E55" s="40" t="s">
+        <v>189</v>
+      </c>
+      <c r="F55" s="34">
+        <v>46140</v>
+      </c>
+      <c r="G55" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="H55" s="34" t="s">
+        <v>290</v>
+      </c>
+      <c r="I55" s="39" t="s">
+        <v>310</v>
+      </c>
+      <c r="J55" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="K55" s="35"/>
+      <c r="L55" s="35"/>
+      <c r="M55" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="N55" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="O55" s="35" t="s">
+        <v>147</v>
+      </c>
+      <c r="P55" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q55" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="R55" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="S55" s="35" t="s">
+        <v>97</v>
+      </c>
+      <c r="T55" s="35"/>
+      <c r="U55" s="36"/>
+      <c r="V55" s="37"/>
+      <c r="W55" s="35" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="56" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F56" s="6"/>
       <c r="G56" s="6"/>
       <c r="H56" s="6"/>
@@ -4985,7 +6103,7 @@
       <c r="V56" s="2"/>
       <c r="W56" s="9"/>
     </row>
-    <row r="57" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F57" s="6"/>
       <c r="G57" s="6"/>
       <c r="H57" s="6"/>
@@ -5005,7 +6123,7 @@
       <c r="V57" s="2"/>
       <c r="W57" s="9"/>
     </row>
-    <row r="58" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F58" s="6"/>
       <c r="G58" s="6"/>
       <c r="H58" s="6"/>
@@ -5025,7 +6143,7 @@
       <c r="V58" s="2"/>
       <c r="W58" s="9"/>
     </row>
-    <row r="59" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F59" s="6"/>
       <c r="G59" s="6"/>
       <c r="H59" s="6"/>
@@ -5045,7 +6163,7 @@
       <c r="V59" s="2"/>
       <c r="W59" s="9"/>
     </row>
-    <row r="60" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F60" s="6"/>
       <c r="G60" s="6"/>
       <c r="H60" s="6"/>
@@ -5065,7 +6183,7 @@
       <c r="V60" s="2"/>
       <c r="W60" s="9"/>
     </row>
-    <row r="61" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F61" s="6"/>
       <c r="G61" s="6"/>
       <c r="H61" s="6"/>
@@ -5085,7 +6203,7 @@
       <c r="V61" s="2"/>
       <c r="W61" s="9"/>
     </row>
-    <row r="62" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F62" s="6"/>
       <c r="G62" s="6"/>
       <c r="H62" s="6"/>
@@ -5105,7 +6223,7 @@
       <c r="V62" s="2"/>
       <c r="W62" s="9"/>
     </row>
-    <row r="63" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F63" s="6"/>
       <c r="G63" s="6"/>
       <c r="H63" s="6"/>
@@ -5125,7 +6243,7 @@
       <c r="V63" s="2"/>
       <c r="W63" s="9"/>
     </row>
-    <row r="64" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F64" s="6"/>
       <c r="G64" s="6"/>
       <c r="H64" s="6"/>
@@ -6745,100 +7863,474 @@
       <c r="V144" s="2"/>
       <c r="W144" s="9"/>
     </row>
-    <row r="145" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W145" s="7"/>
-    </row>
-    <row r="146" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W146" s="7"/>
-    </row>
-    <row r="147" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W147" s="7"/>
-    </row>
-    <row r="148" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W148" s="7"/>
-    </row>
-    <row r="149" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W149" s="7"/>
-    </row>
-    <row r="150" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W150" s="7"/>
-    </row>
-    <row r="151" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W151" s="7"/>
-    </row>
-    <row r="152" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W152" s="7"/>
-    </row>
-    <row r="153" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W153" s="7"/>
-    </row>
-    <row r="154" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W154" s="7"/>
-    </row>
-    <row r="155" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W155" s="7"/>
-    </row>
-    <row r="156" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W156" s="7"/>
-    </row>
-    <row r="157" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W157" s="7"/>
-    </row>
-    <row r="158" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W158" s="7"/>
-    </row>
-    <row r="159" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W159" s="7"/>
-    </row>
-    <row r="160" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W160" s="7"/>
-    </row>
-    <row r="161" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W161" s="7"/>
-    </row>
-    <row r="162" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W162" s="7"/>
-    </row>
-    <row r="163" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W163" s="7"/>
-    </row>
-    <row r="164" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W164" s="7"/>
-    </row>
-    <row r="165" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W165" s="7"/>
-    </row>
-    <row r="166" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W166" s="7"/>
-    </row>
-    <row r="167" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F145" s="6"/>
+      <c r="G145" s="6"/>
+      <c r="H145" s="6"/>
+      <c r="I145" s="6"/>
+      <c r="J145" s="7"/>
+      <c r="K145" s="7"/>
+      <c r="L145" s="7"/>
+      <c r="M145" s="7"/>
+      <c r="N145" s="7"/>
+      <c r="O145" s="7"/>
+      <c r="P145" s="7"/>
+      <c r="Q145" s="7"/>
+      <c r="R145" s="7"/>
+      <c r="S145" s="7"/>
+      <c r="T145" s="7"/>
+      <c r="U145" s="8"/>
+      <c r="V145" s="2"/>
+      <c r="W145" s="9"/>
+    </row>
+    <row r="146" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F146" s="6"/>
+      <c r="G146" s="6"/>
+      <c r="H146" s="6"/>
+      <c r="I146" s="6"/>
+      <c r="J146" s="7"/>
+      <c r="K146" s="7"/>
+      <c r="L146" s="7"/>
+      <c r="M146" s="7"/>
+      <c r="N146" s="7"/>
+      <c r="O146" s="7"/>
+      <c r="P146" s="7"/>
+      <c r="Q146" s="7"/>
+      <c r="R146" s="7"/>
+      <c r="S146" s="7"/>
+      <c r="T146" s="7"/>
+      <c r="U146" s="8"/>
+      <c r="V146" s="2"/>
+      <c r="W146" s="9"/>
+    </row>
+    <row r="147" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F147" s="6"/>
+      <c r="G147" s="6"/>
+      <c r="H147" s="6"/>
+      <c r="I147" s="6"/>
+      <c r="J147" s="7"/>
+      <c r="K147" s="7"/>
+      <c r="L147" s="7"/>
+      <c r="M147" s="7"/>
+      <c r="N147" s="7"/>
+      <c r="O147" s="7"/>
+      <c r="P147" s="7"/>
+      <c r="Q147" s="7"/>
+      <c r="R147" s="7"/>
+      <c r="S147" s="7"/>
+      <c r="T147" s="7"/>
+      <c r="U147" s="8"/>
+      <c r="V147" s="2"/>
+      <c r="W147" s="9"/>
+    </row>
+    <row r="148" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F148" s="6"/>
+      <c r="G148" s="6"/>
+      <c r="H148" s="6"/>
+      <c r="I148" s="6"/>
+      <c r="J148" s="7"/>
+      <c r="K148" s="7"/>
+      <c r="L148" s="7"/>
+      <c r="M148" s="7"/>
+      <c r="N148" s="7"/>
+      <c r="O148" s="7"/>
+      <c r="P148" s="7"/>
+      <c r="Q148" s="7"/>
+      <c r="R148" s="7"/>
+      <c r="S148" s="7"/>
+      <c r="T148" s="7"/>
+      <c r="U148" s="8"/>
+      <c r="V148" s="2"/>
+      <c r="W148" s="9"/>
+    </row>
+    <row r="149" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F149" s="6"/>
+      <c r="G149" s="6"/>
+      <c r="H149" s="6"/>
+      <c r="I149" s="6"/>
+      <c r="J149" s="7"/>
+      <c r="K149" s="7"/>
+      <c r="L149" s="7"/>
+      <c r="M149" s="7"/>
+      <c r="N149" s="7"/>
+      <c r="O149" s="7"/>
+      <c r="P149" s="7"/>
+      <c r="Q149" s="7"/>
+      <c r="R149" s="7"/>
+      <c r="S149" s="7"/>
+      <c r="T149" s="7"/>
+      <c r="U149" s="8"/>
+      <c r="V149" s="2"/>
+      <c r="W149" s="9"/>
+    </row>
+    <row r="150" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F150" s="6"/>
+      <c r="G150" s="6"/>
+      <c r="H150" s="6"/>
+      <c r="I150" s="6"/>
+      <c r="J150" s="7"/>
+      <c r="K150" s="7"/>
+      <c r="L150" s="7"/>
+      <c r="M150" s="7"/>
+      <c r="N150" s="7"/>
+      <c r="O150" s="7"/>
+      <c r="P150" s="7"/>
+      <c r="Q150" s="7"/>
+      <c r="R150" s="7"/>
+      <c r="S150" s="7"/>
+      <c r="T150" s="7"/>
+      <c r="U150" s="8"/>
+      <c r="V150" s="2"/>
+      <c r="W150" s="9"/>
+    </row>
+    <row r="151" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F151" s="6"/>
+      <c r="G151" s="6"/>
+      <c r="H151" s="6"/>
+      <c r="I151" s="6"/>
+      <c r="J151" s="7"/>
+      <c r="K151" s="7"/>
+      <c r="L151" s="7"/>
+      <c r="M151" s="7"/>
+      <c r="N151" s="7"/>
+      <c r="O151" s="7"/>
+      <c r="P151" s="7"/>
+      <c r="Q151" s="7"/>
+      <c r="R151" s="7"/>
+      <c r="S151" s="7"/>
+      <c r="T151" s="7"/>
+      <c r="U151" s="8"/>
+      <c r="V151" s="2"/>
+      <c r="W151" s="9"/>
+    </row>
+    <row r="152" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F152" s="6"/>
+      <c r="G152" s="6"/>
+      <c r="H152" s="6"/>
+      <c r="I152" s="6"/>
+      <c r="J152" s="7"/>
+      <c r="K152" s="7"/>
+      <c r="L152" s="7"/>
+      <c r="M152" s="7"/>
+      <c r="N152" s="7"/>
+      <c r="O152" s="7"/>
+      <c r="P152" s="7"/>
+      <c r="Q152" s="7"/>
+      <c r="R152" s="7"/>
+      <c r="S152" s="7"/>
+      <c r="T152" s="7"/>
+      <c r="U152" s="8"/>
+      <c r="V152" s="2"/>
+      <c r="W152" s="9"/>
+    </row>
+    <row r="153" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F153" s="6"/>
+      <c r="G153" s="6"/>
+      <c r="H153" s="6"/>
+      <c r="I153" s="6"/>
+      <c r="J153" s="7"/>
+      <c r="K153" s="7"/>
+      <c r="L153" s="7"/>
+      <c r="M153" s="7"/>
+      <c r="N153" s="7"/>
+      <c r="O153" s="7"/>
+      <c r="P153" s="7"/>
+      <c r="Q153" s="7"/>
+      <c r="R153" s="7"/>
+      <c r="S153" s="7"/>
+      <c r="T153" s="7"/>
+      <c r="U153" s="8"/>
+      <c r="V153" s="2"/>
+      <c r="W153" s="9"/>
+    </row>
+    <row r="154" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F154" s="6"/>
+      <c r="G154" s="6"/>
+      <c r="H154" s="6"/>
+      <c r="I154" s="6"/>
+      <c r="J154" s="7"/>
+      <c r="K154" s="7"/>
+      <c r="L154" s="7"/>
+      <c r="M154" s="7"/>
+      <c r="N154" s="7"/>
+      <c r="O154" s="7"/>
+      <c r="P154" s="7"/>
+      <c r="Q154" s="7"/>
+      <c r="R154" s="7"/>
+      <c r="S154" s="7"/>
+      <c r="T154" s="7"/>
+      <c r="U154" s="8"/>
+      <c r="V154" s="2"/>
+      <c r="W154" s="9"/>
+    </row>
+    <row r="155" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F155" s="6"/>
+      <c r="G155" s="6"/>
+      <c r="H155" s="6"/>
+      <c r="I155" s="6"/>
+      <c r="J155" s="7"/>
+      <c r="K155" s="7"/>
+      <c r="L155" s="7"/>
+      <c r="M155" s="7"/>
+      <c r="N155" s="7"/>
+      <c r="O155" s="7"/>
+      <c r="P155" s="7"/>
+      <c r="Q155" s="7"/>
+      <c r="R155" s="7"/>
+      <c r="S155" s="7"/>
+      <c r="T155" s="7"/>
+      <c r="U155" s="8"/>
+      <c r="V155" s="2"/>
+      <c r="W155" s="9"/>
+    </row>
+    <row r="156" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F156" s="6"/>
+      <c r="G156" s="6"/>
+      <c r="H156" s="6"/>
+      <c r="I156" s="6"/>
+      <c r="J156" s="7"/>
+      <c r="K156" s="7"/>
+      <c r="L156" s="7"/>
+      <c r="M156" s="7"/>
+      <c r="N156" s="7"/>
+      <c r="O156" s="7"/>
+      <c r="P156" s="7"/>
+      <c r="Q156" s="7"/>
+      <c r="R156" s="7"/>
+      <c r="S156" s="7"/>
+      <c r="T156" s="7"/>
+      <c r="U156" s="8"/>
+      <c r="V156" s="2"/>
+      <c r="W156" s="9"/>
+    </row>
+    <row r="157" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F157" s="6"/>
+      <c r="G157" s="6"/>
+      <c r="H157" s="6"/>
+      <c r="I157" s="6"/>
+      <c r="J157" s="7"/>
+      <c r="K157" s="7"/>
+      <c r="L157" s="7"/>
+      <c r="M157" s="7"/>
+      <c r="N157" s="7"/>
+      <c r="O157" s="7"/>
+      <c r="P157" s="7"/>
+      <c r="Q157" s="7"/>
+      <c r="R157" s="7"/>
+      <c r="S157" s="7"/>
+      <c r="T157" s="7"/>
+      <c r="U157" s="8"/>
+      <c r="V157" s="2"/>
+      <c r="W157" s="9"/>
+    </row>
+    <row r="158" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F158" s="6"/>
+      <c r="G158" s="6"/>
+      <c r="H158" s="6"/>
+      <c r="I158" s="6"/>
+      <c r="J158" s="7"/>
+      <c r="K158" s="7"/>
+      <c r="L158" s="7"/>
+      <c r="M158" s="7"/>
+      <c r="N158" s="7"/>
+      <c r="O158" s="7"/>
+      <c r="P158" s="7"/>
+      <c r="Q158" s="7"/>
+      <c r="R158" s="7"/>
+      <c r="S158" s="7"/>
+      <c r="T158" s="7"/>
+      <c r="U158" s="8"/>
+      <c r="V158" s="2"/>
+      <c r="W158" s="9"/>
+    </row>
+    <row r="159" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F159" s="6"/>
+      <c r="G159" s="6"/>
+      <c r="H159" s="6"/>
+      <c r="I159" s="6"/>
+      <c r="J159" s="7"/>
+      <c r="K159" s="7"/>
+      <c r="L159" s="7"/>
+      <c r="M159" s="7"/>
+      <c r="N159" s="7"/>
+      <c r="O159" s="7"/>
+      <c r="P159" s="7"/>
+      <c r="Q159" s="7"/>
+      <c r="R159" s="7"/>
+      <c r="S159" s="7"/>
+      <c r="T159" s="7"/>
+      <c r="U159" s="8"/>
+      <c r="V159" s="2"/>
+      <c r="W159" s="9"/>
+    </row>
+    <row r="160" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F160" s="6"/>
+      <c r="G160" s="6"/>
+      <c r="H160" s="6"/>
+      <c r="I160" s="6"/>
+      <c r="J160" s="7"/>
+      <c r="K160" s="7"/>
+      <c r="L160" s="7"/>
+      <c r="M160" s="7"/>
+      <c r="N160" s="7"/>
+      <c r="O160" s="7"/>
+      <c r="P160" s="7"/>
+      <c r="Q160" s="7"/>
+      <c r="R160" s="7"/>
+      <c r="S160" s="7"/>
+      <c r="T160" s="7"/>
+      <c r="U160" s="8"/>
+      <c r="V160" s="2"/>
+      <c r="W160" s="9"/>
+    </row>
+    <row r="161" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F161" s="6"/>
+      <c r="G161" s="6"/>
+      <c r="H161" s="6"/>
+      <c r="I161" s="6"/>
+      <c r="J161" s="7"/>
+      <c r="K161" s="7"/>
+      <c r="L161" s="7"/>
+      <c r="M161" s="7"/>
+      <c r="N161" s="7"/>
+      <c r="O161" s="7"/>
+      <c r="P161" s="7"/>
+      <c r="Q161" s="7"/>
+      <c r="R161" s="7"/>
+      <c r="S161" s="7"/>
+      <c r="T161" s="7"/>
+      <c r="U161" s="8"/>
+      <c r="V161" s="2"/>
+      <c r="W161" s="9"/>
+    </row>
+    <row r="162" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F162" s="6"/>
+      <c r="G162" s="6"/>
+      <c r="H162" s="6"/>
+      <c r="I162" s="6"/>
+      <c r="J162" s="7"/>
+      <c r="K162" s="7"/>
+      <c r="L162" s="7"/>
+      <c r="M162" s="7"/>
+      <c r="N162" s="7"/>
+      <c r="O162" s="7"/>
+      <c r="P162" s="7"/>
+      <c r="Q162" s="7"/>
+      <c r="R162" s="7"/>
+      <c r="S162" s="7"/>
+      <c r="T162" s="7"/>
+      <c r="U162" s="8"/>
+      <c r="V162" s="2"/>
+      <c r="W162" s="9"/>
+    </row>
+    <row r="163" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F163" s="6"/>
+      <c r="G163" s="6"/>
+      <c r="H163" s="6"/>
+      <c r="I163" s="6"/>
+      <c r="J163" s="7"/>
+      <c r="K163" s="7"/>
+      <c r="L163" s="7"/>
+      <c r="M163" s="7"/>
+      <c r="N163" s="7"/>
+      <c r="O163" s="7"/>
+      <c r="P163" s="7"/>
+      <c r="Q163" s="7"/>
+      <c r="R163" s="7"/>
+      <c r="S163" s="7"/>
+      <c r="T163" s="7"/>
+      <c r="U163" s="8"/>
+      <c r="V163" s="2"/>
+      <c r="W163" s="9"/>
+    </row>
+    <row r="164" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F164" s="6"/>
+      <c r="G164" s="6"/>
+      <c r="H164" s="6"/>
+      <c r="I164" s="6"/>
+      <c r="J164" s="7"/>
+      <c r="K164" s="7"/>
+      <c r="L164" s="7"/>
+      <c r="M164" s="7"/>
+      <c r="N164" s="7"/>
+      <c r="O164" s="7"/>
+      <c r="P164" s="7"/>
+      <c r="Q164" s="7"/>
+      <c r="R164" s="7"/>
+      <c r="S164" s="7"/>
+      <c r="T164" s="7"/>
+      <c r="U164" s="8"/>
+      <c r="V164" s="2"/>
+      <c r="W164" s="9"/>
+    </row>
+    <row r="165" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F165" s="6"/>
+      <c r="G165" s="6"/>
+      <c r="H165" s="6"/>
+      <c r="I165" s="6"/>
+      <c r="J165" s="7"/>
+      <c r="K165" s="7"/>
+      <c r="L165" s="7"/>
+      <c r="M165" s="7"/>
+      <c r="N165" s="7"/>
+      <c r="O165" s="7"/>
+      <c r="P165" s="7"/>
+      <c r="Q165" s="7"/>
+      <c r="R165" s="7"/>
+      <c r="S165" s="7"/>
+      <c r="T165" s="7"/>
+      <c r="U165" s="8"/>
+      <c r="V165" s="2"/>
+      <c r="W165" s="9"/>
+    </row>
+    <row r="166" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F166" s="6"/>
+      <c r="G166" s="6"/>
+      <c r="H166" s="6"/>
+      <c r="I166" s="6"/>
+      <c r="J166" s="7"/>
+      <c r="K166" s="7"/>
+      <c r="L166" s="7"/>
+      <c r="M166" s="7"/>
+      <c r="N166" s="7"/>
+      <c r="O166" s="7"/>
+      <c r="P166" s="7"/>
+      <c r="Q166" s="7"/>
+      <c r="R166" s="7"/>
+      <c r="S166" s="7"/>
+      <c r="T166" s="7"/>
+      <c r="U166" s="8"/>
+      <c r="V166" s="2"/>
+      <c r="W166" s="9"/>
+    </row>
+    <row r="167" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="W167" s="7"/>
     </row>
-    <row r="168" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="W168" s="7"/>
     </row>
-    <row r="169" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="W169" s="7"/>
     </row>
-    <row r="170" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="W170" s="7"/>
     </row>
-    <row r="171" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="W171" s="7"/>
     </row>
-    <row r="172" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="W172" s="7"/>
     </row>
-    <row r="173" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="W173" s="7"/>
     </row>
-    <row r="174" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="W174" s="7"/>
     </row>
-    <row r="175" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="W175" s="7"/>
     </row>
-    <row r="176" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="W176" s="7"/>
     </row>
     <row r="177" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7996,15 +9488,81 @@
     <row r="561" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="W561" s="7"/>
     </row>
-    <row r="562" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="563" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="564" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="565" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="566" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="562" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W562" s="7"/>
+    </row>
+    <row r="563" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W563" s="7"/>
+    </row>
+    <row r="564" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W564" s="7"/>
+    </row>
+    <row r="565" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W565" s="7"/>
+    </row>
+    <row r="566" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W566" s="7"/>
+    </row>
+    <row r="567" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W567" s="7"/>
+    </row>
+    <row r="568" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W568" s="7"/>
+    </row>
+    <row r="569" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W569" s="7"/>
+    </row>
+    <row r="570" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W570" s="7"/>
+    </row>
+    <row r="571" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W571" s="7"/>
+    </row>
+    <row r="572" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W572" s="7"/>
+    </row>
+    <row r="573" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W573" s="7"/>
+    </row>
+    <row r="574" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W574" s="7"/>
+    </row>
+    <row r="575" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W575" s="7"/>
+    </row>
+    <row r="576" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W576" s="7"/>
+    </row>
+    <row r="577" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W577" s="7"/>
+    </row>
+    <row r="578" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W578" s="7"/>
+    </row>
+    <row r="579" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W579" s="7"/>
+    </row>
+    <row r="580" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W580" s="7"/>
+    </row>
+    <row r="581" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W581" s="7"/>
+    </row>
+    <row r="582" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W582" s="7"/>
+    </row>
+    <row r="583" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W583" s="7"/>
+    </row>
+    <row r="584" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="585" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="586" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="587" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="588" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A9:W32" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A10:W32">
-    <sortCondition ref="A10:A32"/>
+  <autoFilter ref="A9:W55" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A10:W54">
+    <sortCondition ref="A10:A54"/>
   </sortState>
   <mergeCells count="7">
     <mergeCell ref="A6:B6"/>
@@ -8017,10 +9575,10 @@
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="J31:J32 P31:R32 M31:N32 M29:N29 P29:R29 T29:T32" xr:uid="{00000000-0002-0000-0200-000004000000}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="P53:R55 M53:N55 T49:T55 M50:N51 R49:R51 P32:Q51" xr:uid="{00000000-0002-0000-0200-000004000000}"/>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" fitToWidth="6" fitToHeight="0" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
@@ -8029,19 +9587,19 @@
           <x14:formula1>
             <xm:f>Sheet1!$B$2:$B$3</xm:f>
           </x14:formula1>
-          <xm:sqref>P30:R30 M30:N30 P10:R28 M10:N28 J10:J30</xm:sqref>
+          <xm:sqref>P52:R52 M52:N52 M10:N49 J10:J55 R10:R48 P10:Q31</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0200-000002000000}">
           <x14:formula1>
             <xm:f>'LISTA VALORI'!$A$2:$A$8</xm:f>
           </x14:formula1>
-          <xm:sqref>K10:K32</xm:sqref>
+          <xm:sqref>K12:K31 K36:K38 K10 K48:K55</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0200-000001000000}">
           <x14:formula1>
             <xm:f>Sheet1!$A$2:$A$3</xm:f>
           </x14:formula1>
-          <xm:sqref>T10:T28</xm:sqref>
+          <xm:sqref>T10:T48</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -10285,18 +11843,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="a56712a3-8dfd-4688-917a-22f0cf513b89" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <UserStoryALM xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A92AB09DCDF6014AA0D6826BF29E2C8E" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d4db60622090a1f8a8d506ac1d64a349">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1e76d14e-d0ce-457c-8343-9b55836d9ead" xmlns:ns3="a56712a3-8dfd-4688-917a-22f0cf513b89" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0a3a9ed8bb952a3d76dd1e2fa3d624b9" ns2:_="" ns3:_="">
     <xsd:import namespace="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
@@ -10554,6 +12100,18 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="a56712a3-8dfd-4688-917a-22f0cf513b89" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <UserStoryALM xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -10564,23 +12122,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ACB08642-5694-4F88-BF6F-98521E3A5E0B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10599,6 +12140,23 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
   <ds:schemaRefs>
